--- a/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>2.23</v>
+        <v>2.472</v>
       </c>
       <c r="D16">
-        <v>1.012</v>
+        <v>1.464</v>
       </c>
       <c r="E16">
-        <v>3.447</v>
+        <v>3.481</v>
       </c>
       <c r="F16">
-        <v>9.763</v>
+        <v>10.825</v>
       </c>
       <c r="G16">
-        <v>4.392</v>
+        <v>6.352</v>
       </c>
       <c r="H16">
-        <v>15.134</v>
+        <v>15.299</v>
       </c>
       <c r="I16">
-        <v>104720.483</v>
+        <v>116119.469</v>
       </c>
       <c r="J16">
-        <v>47542.542</v>
+        <v>68744.614</v>
       </c>
       <c r="K16">
-        <v>161898.424</v>
+        <v>163494.324</v>
       </c>
       <c r="L16">
-        <v>1298514.453</v>
+        <v>1439747.589</v>
       </c>
       <c r="M16">
-        <v>584184.596</v>
+        <v>844749.856</v>
       </c>
       <c r="N16">
-        <v>2012844.31</v>
+        <v>2034745.322</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>67.5</v>
+        <v>74.79900000000001</v>
       </c>
       <c r="D17">
-        <v>32.933</v>
+        <v>47.421</v>
       </c>
       <c r="E17">
-        <v>102.066</v>
+        <v>102.178</v>
       </c>
       <c r="F17">
-        <v>259.222</v>
+        <v>287.244</v>
       </c>
       <c r="G17">
-        <v>126.18</v>
+        <v>181.849</v>
       </c>
       <c r="H17">
-        <v>392.264</v>
+        <v>392.639</v>
       </c>
       <c r="I17">
-        <v>3170317.057</v>
+        <v>3513167.551</v>
       </c>
       <c r="J17">
-        <v>1546800.942</v>
+        <v>2227260.468</v>
       </c>
       <c r="K17">
-        <v>4793833.171</v>
+        <v>4799074.635</v>
       </c>
       <c r="L17">
-        <v>34476520.804</v>
+        <v>38203445.769</v>
       </c>
       <c r="M17">
-        <v>16781968.56</v>
+        <v>24185954.095</v>
       </c>
       <c r="N17">
-        <v>52171073.048</v>
+        <v>52220937.442</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>337.334</v>
+        <v>372.437</v>
       </c>
       <c r="D18">
-        <v>179.499</v>
+        <v>252.948</v>
       </c>
       <c r="E18">
-        <v>495.17</v>
+        <v>491.926</v>
       </c>
       <c r="F18">
-        <v>1075.026</v>
+        <v>1186.862</v>
       </c>
       <c r="G18">
-        <v>570.995</v>
+        <v>803.999</v>
       </c>
       <c r="H18">
-        <v>1579.058</v>
+        <v>1569.726</v>
       </c>
       <c r="I18">
-        <v>15843918.819</v>
+        <v>17492623.809</v>
       </c>
       <c r="J18">
-        <v>8430690.064999999</v>
+        <v>11880463.72</v>
       </c>
       <c r="K18">
-        <v>23257147.574</v>
+        <v>23104783.899</v>
       </c>
       <c r="L18">
-        <v>142978474.583</v>
+        <v>157852707.535</v>
       </c>
       <c r="M18">
-        <v>75942296.433</v>
+        <v>106931862.162</v>
       </c>
       <c r="N18">
-        <v>210014652.732</v>
+        <v>208773552.908</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>466.025</v>
+        <v>516.116</v>
       </c>
       <c r="D19">
-        <v>239.373</v>
+        <v>344.582</v>
       </c>
       <c r="E19">
-        <v>692.677</v>
+        <v>687.649</v>
       </c>
       <c r="F19">
-        <v>1154.94</v>
+        <v>1279.172</v>
       </c>
       <c r="G19">
-        <v>591.274</v>
+        <v>851.182</v>
       </c>
       <c r="H19">
-        <v>1718.605</v>
+        <v>1707.161</v>
       </c>
       <c r="I19">
-        <v>21888264.161</v>
+        <v>24240913.026</v>
       </c>
       <c r="J19">
-        <v>11242881.628</v>
+        <v>16184344.278</v>
       </c>
       <c r="K19">
-        <v>32533646.695</v>
+        <v>32297481.773</v>
       </c>
       <c r="L19">
-        <v>153607000.157</v>
+        <v>170129852.653</v>
       </c>
       <c r="M19">
-        <v>78639484.13</v>
+        <v>113207268.883</v>
       </c>
       <c r="N19">
-        <v>228574516.183</v>
+        <v>227052436.423</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>927.6130000000001</v>
+        <v>1025.589</v>
       </c>
       <c r="D20">
-        <v>491.187</v>
+        <v>699.665</v>
       </c>
       <c r="E20">
-        <v>1364.039</v>
+        <v>1351.514</v>
       </c>
       <c r="F20">
-        <v>1659.63</v>
+        <v>1834.767</v>
       </c>
       <c r="G20">
-        <v>876.266</v>
+        <v>1245.353</v>
       </c>
       <c r="H20">
-        <v>2442.993</v>
+        <v>2424.181</v>
       </c>
       <c r="I20">
-        <v>43568131.458</v>
+        <v>48169882.636</v>
       </c>
       <c r="J20">
-        <v>23070075.34</v>
+        <v>32861849.954</v>
       </c>
       <c r="K20">
-        <v>64066187.576</v>
+        <v>63477915.319</v>
       </c>
       <c r="L20">
-        <v>220730770.568</v>
+        <v>244023997.532</v>
       </c>
       <c r="M20">
-        <v>116543429.164</v>
+        <v>165631946.6</v>
       </c>
       <c r="N20">
-        <v>324918111.972</v>
+        <v>322416048.463</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>1147.051</v>
+        <v>1270.363</v>
       </c>
       <c r="D21">
-        <v>602.082</v>
+        <v>866.614</v>
       </c>
       <c r="E21">
-        <v>1692.02</v>
+        <v>1674.111</v>
       </c>
       <c r="F21">
-        <v>1289.334</v>
+        <v>1427.605</v>
       </c>
       <c r="G21">
-        <v>678.046</v>
+        <v>975.631</v>
       </c>
       <c r="H21">
-        <v>1900.623</v>
+        <v>1879.58</v>
       </c>
       <c r="I21">
-        <v>53874702.934</v>
+        <v>59666388.502</v>
       </c>
       <c r="J21">
-        <v>28278600.555</v>
+        <v>40703137.995</v>
       </c>
       <c r="K21">
-        <v>79470805.31200001</v>
+        <v>78629639.009</v>
       </c>
       <c r="L21">
-        <v>171481488.252</v>
+        <v>189871496.728</v>
       </c>
       <c r="M21">
-        <v>90180176.582</v>
+        <v>129758861.358</v>
       </c>
       <c r="N21">
-        <v>252782799.922</v>
+        <v>249984132.097</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>644.855</v>
+        <v>715.8339999999999</v>
       </c>
       <c r="D22">
-        <v>342.227</v>
+        <v>503.563</v>
       </c>
       <c r="E22">
-        <v>947.482</v>
+        <v>928.104</v>
       </c>
       <c r="F22">
-        <v>221.447</v>
+        <v>246.107</v>
       </c>
       <c r="G22">
-        <v>112.846</v>
+        <v>167.042</v>
       </c>
       <c r="H22">
-        <v>330.048</v>
+        <v>325.172</v>
       </c>
       <c r="I22">
-        <v>30287539.737</v>
+        <v>33621285.815</v>
       </c>
       <c r="J22">
-        <v>16073734.052</v>
+        <v>23651369.772</v>
       </c>
       <c r="K22">
-        <v>44501345.422</v>
+        <v>43591201.859</v>
       </c>
       <c r="L22">
-        <v>29452503.263</v>
+        <v>32732232.572</v>
       </c>
       <c r="M22">
-        <v>15008562.086</v>
+        <v>22216581.039</v>
       </c>
       <c r="N22">
-        <v>43896444.44</v>
+        <v>43247884.105</v>
       </c>
     </row>
     <row r="23">
@@ -2463,13 +2463,13 @@
         <v>22702.549</v>
       </c>
       <c r="F44">
-        <v>172043.126</v>
+        <v>28673.854</v>
       </c>
       <c r="G44">
-        <v>95919.125</v>
+        <v>15986.521</v>
       </c>
       <c r="H44">
-        <v>248167.127</v>
+        <v>41361.188</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>22881735733.381</v>
+        <v>3813622622.23</v>
       </c>
       <c r="M44">
-        <v>12757243570.997</v>
+        <v>2126207261.833</v>
       </c>
       <c r="N44">
-        <v>33006227895.764</v>
+        <v>5501037982.627</v>
       </c>
     </row>
     <row r="45">
@@ -2511,13 +2511,13 @@
         <v>50528.316</v>
       </c>
       <c r="F45">
-        <v>345410.177</v>
+        <v>57568.363</v>
       </c>
       <c r="G45">
-        <v>206193.856</v>
+        <v>34365.643</v>
       </c>
       <c r="H45">
-        <v>484626.497</v>
+        <v>80771.083</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2529,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>45939553489.09</v>
+        <v>7656592248.182</v>
       </c>
       <c r="M45">
-        <v>27423782831.3</v>
+        <v>4570630471.883</v>
       </c>
       <c r="N45">
-        <v>64455324146.879</v>
+        <v>10742554024.48</v>
       </c>
     </row>
     <row r="46">
@@ -2559,13 +2559,13 @@
         <v>59505.237</v>
       </c>
       <c r="F46">
-        <v>329993.604</v>
+        <v>54998.934</v>
       </c>
       <c r="G46">
-        <v>196319.26</v>
+        <v>32719.877</v>
       </c>
       <c r="H46">
-        <v>463667.947</v>
+        <v>77277.99099999999</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>43889149275.653</v>
+        <v>7314858212.609</v>
       </c>
       <c r="M46">
-        <v>26110461621.14</v>
+        <v>4351743603.523</v>
       </c>
       <c r="N46">
-        <v>61667836930.165</v>
+        <v>10277972821.694</v>
       </c>
     </row>
     <row r="47">
@@ -2607,13 +2607,13 @@
         <v>34327.633</v>
       </c>
       <c r="F47">
-        <v>148238.782</v>
+        <v>24706.464</v>
       </c>
       <c r="G47">
-        <v>88822.789</v>
+        <v>14803.798</v>
       </c>
       <c r="H47">
-        <v>207654.775</v>
+        <v>34609.129</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>19715757973.226</v>
+        <v>3285959662.204</v>
       </c>
       <c r="M47">
-        <v>11813430927.176</v>
+        <v>1968905154.529</v>
       </c>
       <c r="N47">
-        <v>27618085019.275</v>
+        <v>4603014169.879</v>
       </c>
     </row>
     <row r="48">
@@ -2655,13 +2655,13 @@
         <v>51114.456</v>
       </c>
       <c r="F48">
-        <v>159240.779</v>
+        <v>26540.13</v>
       </c>
       <c r="G48">
-        <v>97589.387</v>
+        <v>16264.898</v>
       </c>
       <c r="H48">
-        <v>220892.172</v>
+        <v>36815.362</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>21179023664.71</v>
+        <v>3529837277.452</v>
       </c>
       <c r="M48">
-        <v>12979388484.664</v>
+        <v>2163231414.111</v>
       </c>
       <c r="N48">
-        <v>29378658844.757</v>
+        <v>4896443140.793</v>
       </c>
     </row>
     <row r="49">
@@ -2703,13 +2703,13 @@
         <v>30358.498</v>
       </c>
       <c r="F49">
-        <v>58060.532</v>
+        <v>9676.754999999999</v>
       </c>
       <c r="G49">
-        <v>35765.142</v>
+        <v>5960.857</v>
       </c>
       <c r="H49">
-        <v>80355.92200000001</v>
+        <v>13392.654</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>7722050776.568</v>
+        <v>1287008462.761</v>
       </c>
       <c r="M49">
-        <v>4756763920.139</v>
+        <v>792793986.6900001</v>
       </c>
       <c r="N49">
-        <v>10687337632.997</v>
+        <v>1781222938.833</v>
       </c>
     </row>
     <row r="50">

--- a/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
@@ -447,13 +447,13 @@
         <v>146.027</v>
       </c>
       <c r="F2">
-        <v>6295.986</v>
+        <v>1049.331</v>
       </c>
       <c r="G2">
-        <v>3896.906</v>
+        <v>649.484</v>
       </c>
       <c r="H2">
-        <v>8695.066999999999</v>
+        <v>1449.178</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>837366203.476</v>
+        <v>139561033.913</v>
       </c>
       <c r="M2">
-        <v>518288450.495</v>
+        <v>86381408.41599999</v>
       </c>
       <c r="N2">
-        <v>1156443956.457</v>
+        <v>192740659.409</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>368.618</v>
       </c>
       <c r="F3">
-        <v>14156.403</v>
+        <v>2359.401</v>
       </c>
       <c r="G3">
-        <v>9209.032999999999</v>
+        <v>1534.839</v>
       </c>
       <c r="H3">
-        <v>19103.774</v>
+        <v>3183.962</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1882801624.89</v>
+        <v>313800270.815</v>
       </c>
       <c r="M3">
-        <v>1224801330.221</v>
+        <v>204133555.037</v>
       </c>
       <c r="N3">
-        <v>2540801919.559</v>
+        <v>423466986.593</v>
       </c>
     </row>
     <row r="4">
@@ -543,13 +543,13 @@
         <v>1178.415</v>
       </c>
       <c r="F4">
-        <v>35331.192</v>
+        <v>5888.532</v>
       </c>
       <c r="G4">
-        <v>22228.029</v>
+        <v>3704.671</v>
       </c>
       <c r="H4">
-        <v>48434.355</v>
+        <v>8072.393</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>4699048504.234</v>
+        <v>783174750.706</v>
       </c>
       <c r="M4">
-        <v>2956327792.023</v>
+        <v>492721298.67</v>
       </c>
       <c r="N4">
-        <v>6441769216.444</v>
+        <v>1073628202.741</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>2052.977</v>
       </c>
       <c r="F5">
-        <v>47647.175</v>
+        <v>7941.196</v>
       </c>
       <c r="G5">
-        <v>30632.846</v>
+        <v>5105.474</v>
       </c>
       <c r="H5">
-        <v>64661.505</v>
+        <v>10776.917</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6337074285.643</v>
+        <v>1056179047.607</v>
       </c>
       <c r="M5">
-        <v>4074168459.644</v>
+        <v>679028076.607</v>
       </c>
       <c r="N5">
-        <v>8599980111.641001</v>
+        <v>1433330018.607</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>6200.597</v>
       </c>
       <c r="F6">
-        <v>100850.939</v>
+        <v>16808.49</v>
       </c>
       <c r="G6">
-        <v>67658.99800000001</v>
+        <v>11276.5</v>
       </c>
       <c r="H6">
-        <v>134042.88</v>
+        <v>22340.48</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>13413174875.843</v>
+        <v>2235529145.974</v>
       </c>
       <c r="M6">
-        <v>8998646692.312</v>
+        <v>1499774448.719</v>
       </c>
       <c r="N6">
-        <v>17827703059.375</v>
+        <v>2971283843.229</v>
       </c>
     </row>
     <row r="7">
@@ -687,13 +687,13 @@
         <v>12033.17</v>
       </c>
       <c r="F7">
-        <v>104130.828</v>
+        <v>17355.138</v>
       </c>
       <c r="G7">
-        <v>70039.923</v>
+        <v>11673.32</v>
       </c>
       <c r="H7">
-        <v>138221.733</v>
+        <v>23036.956</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>13849400127.746</v>
+        <v>2308233354.624</v>
       </c>
       <c r="M7">
-        <v>9315309749.16</v>
+        <v>1552551624.86</v>
       </c>
       <c r="N7">
-        <v>18383490506.331</v>
+        <v>3063915084.388</v>
       </c>
     </row>
     <row r="8">
@@ -735,13 +735,13 @@
         <v>27868.315</v>
       </c>
       <c r="F8">
-        <v>36169.682</v>
+        <v>6028.28</v>
       </c>
       <c r="G8">
-        <v>23607.031</v>
+        <v>3934.505</v>
       </c>
       <c r="H8">
-        <v>48732.332</v>
+        <v>8122.055</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>4810567644.211</v>
+        <v>801761274.035</v>
       </c>
       <c r="M8">
-        <v>3139735151.55</v>
+        <v>523289191.925</v>
       </c>
       <c r="N8">
-        <v>6481400136.872</v>
+        <v>1080233356.145</v>
       </c>
     </row>
     <row r="9">
@@ -783,31 +783,31 @@
         <v>43.534</v>
       </c>
       <c r="F9">
-        <v>93.669</v>
+        <v>19.291</v>
       </c>
       <c r="G9">
-        <v>45.913</v>
+        <v>9.462999999999999</v>
       </c>
       <c r="H9">
-        <v>141.425</v>
+        <v>29.118</v>
       </c>
       <c r="I9">
-        <v>604367.09</v>
+        <v>1607816.202</v>
       </c>
       <c r="J9">
-        <v>297223.326</v>
+        <v>790712.28</v>
       </c>
       <c r="K9">
-        <v>911510.8540000001</v>
+        <v>2424920.125</v>
       </c>
       <c r="L9">
-        <v>12457939.383</v>
+        <v>2565657.509</v>
       </c>
       <c r="M9">
-        <v>6106370.833</v>
+        <v>1258605.375</v>
       </c>
       <c r="N9">
-        <v>18809507.932</v>
+        <v>3872709.642</v>
       </c>
     </row>
     <row r="10">
@@ -831,31 +831,31 @@
         <v>110.005</v>
       </c>
       <c r="F10">
-        <v>209.88</v>
+        <v>43.205</v>
       </c>
       <c r="G10">
-        <v>109.217</v>
+        <v>22.493</v>
       </c>
       <c r="H10">
-        <v>310.543</v>
+        <v>63.917</v>
       </c>
       <c r="I10">
-        <v>1557738.821</v>
+        <v>4144100.095</v>
       </c>
       <c r="J10">
-        <v>812198.0600000001</v>
+        <v>2160715.272</v>
       </c>
       <c r="K10">
-        <v>2303279.581</v>
+        <v>6127484.918</v>
       </c>
       <c r="L10">
-        <v>27914041.051</v>
+        <v>5746247.378</v>
       </c>
       <c r="M10">
-        <v>14525825.211</v>
+        <v>2991582.443</v>
       </c>
       <c r="N10">
-        <v>41302256.891</v>
+        <v>8500912.312999999</v>
       </c>
     </row>
     <row r="11">
@@ -879,31 +879,31 @@
         <v>398.242</v>
       </c>
       <c r="F11">
-        <v>587.3099999999999</v>
+        <v>120.929</v>
       </c>
       <c r="G11">
-        <v>293.222</v>
+        <v>60.31</v>
       </c>
       <c r="H11">
-        <v>881.398</v>
+        <v>181.547</v>
       </c>
       <c r="I11">
-        <v>5545834.812</v>
+        <v>14753753.497</v>
       </c>
       <c r="J11">
-        <v>2753272.875</v>
+        <v>7324615.803</v>
       </c>
       <c r="K11">
-        <v>8338396.749</v>
+        <v>22182891.19</v>
       </c>
       <c r="L11">
-        <v>78112210.84100001</v>
+        <v>16083492.198</v>
       </c>
       <c r="M11">
-        <v>38998522.48</v>
+        <v>8021289.565</v>
       </c>
       <c r="N11">
-        <v>117225899.201</v>
+        <v>24145694.831</v>
       </c>
     </row>
     <row r="12">
@@ -927,31 +927,31 @@
         <v>866.069</v>
       </c>
       <c r="F12">
-        <v>981.2910000000001</v>
+        <v>202.021</v>
       </c>
       <c r="G12">
-        <v>501.737</v>
+        <v>103.348</v>
       </c>
       <c r="H12">
-        <v>1460.845</v>
+        <v>300.695</v>
       </c>
       <c r="I12">
-        <v>12180892.028</v>
+        <v>32405198.574</v>
       </c>
       <c r="J12">
-        <v>6228032.23</v>
+        <v>16568624.094</v>
       </c>
       <c r="K12">
-        <v>18133751.826</v>
+        <v>48241773.054</v>
       </c>
       <c r="L12">
-        <v>130511724.44</v>
+        <v>26868830.494</v>
       </c>
       <c r="M12">
-        <v>66731015.841</v>
+        <v>13745227.084</v>
       </c>
       <c r="N12">
-        <v>194292433.039</v>
+        <v>39992433.904</v>
       </c>
     </row>
     <row r="13">
@@ -975,31 +975,31 @@
         <v>3140.92</v>
       </c>
       <c r="F13">
-        <v>2516.781</v>
+        <v>518.202</v>
       </c>
       <c r="G13">
-        <v>1374.34</v>
+        <v>282.861</v>
       </c>
       <c r="H13">
-        <v>3659.223</v>
+        <v>753.544</v>
       </c>
       <c r="I13">
-        <v>45332315.83</v>
+        <v>120598942.419</v>
       </c>
       <c r="J13">
-        <v>24900042.436</v>
+        <v>66242342.332</v>
       </c>
       <c r="K13">
-        <v>65764589.224</v>
+        <v>174955542.505</v>
       </c>
       <c r="L13">
-        <v>334731908.18</v>
+        <v>68920889.17200001</v>
       </c>
       <c r="M13">
-        <v>182787173.314</v>
+        <v>37620450.725</v>
       </c>
       <c r="N13">
-        <v>486676643.047</v>
+        <v>100221327.619</v>
       </c>
     </row>
     <row r="14">
@@ -1023,31 +1023,31 @@
         <v>5327.87</v>
       </c>
       <c r="F14">
-        <v>2444.937</v>
+        <v>503.405</v>
       </c>
       <c r="G14">
-        <v>1336.133</v>
+        <v>275.121</v>
       </c>
       <c r="H14">
-        <v>3553.741</v>
+        <v>731.689</v>
       </c>
       <c r="I14">
-        <v>76720125.96699999</v>
+        <v>204100891.041</v>
       </c>
       <c r="J14">
-        <v>41885311.057</v>
+        <v>111428770.49</v>
       </c>
       <c r="K14">
-        <v>111554940.877</v>
+        <v>296773011.592</v>
       </c>
       <c r="L14">
-        <v>325176624.98</v>
+        <v>66952841.036</v>
       </c>
       <c r="M14">
-        <v>177705696.963</v>
+        <v>36591060.271</v>
       </c>
       <c r="N14">
-        <v>472647552.997</v>
+        <v>97314621.801</v>
       </c>
     </row>
     <row r="15">
@@ -1071,31 +1071,31 @@
         <v>5457.221</v>
       </c>
       <c r="F15">
-        <v>595.609</v>
+        <v>122.625</v>
       </c>
       <c r="G15">
-        <v>295.772</v>
+        <v>60.944</v>
       </c>
       <c r="H15">
-        <v>895.447</v>
+        <v>184.307</v>
       </c>
       <c r="I15">
-        <v>77480546.777</v>
+        <v>206123861.715</v>
       </c>
       <c r="J15">
-        <v>40697798.374</v>
+        <v>108269594.279</v>
       </c>
       <c r="K15">
-        <v>114263295.181</v>
+        <v>303978129.15</v>
       </c>
       <c r="L15">
-        <v>79216054.38</v>
+        <v>16309185.37</v>
       </c>
       <c r="M15">
-        <v>39337670.285</v>
+        <v>8105531.188</v>
       </c>
       <c r="N15">
-        <v>119094438.475</v>
+        <v>24512839.551</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>2.472</v>
+        <v>0.484</v>
       </c>
       <c r="D16">
-        <v>1.464</v>
+        <v>-0.034</v>
       </c>
       <c r="E16">
-        <v>3.481</v>
+        <v>1.002</v>
       </c>
       <c r="F16">
-        <v>10.825</v>
+        <v>0.361</v>
       </c>
       <c r="G16">
-        <v>6.352</v>
+        <v>-0.027</v>
       </c>
       <c r="H16">
-        <v>15.299</v>
+        <v>0.748</v>
       </c>
       <c r="I16">
-        <v>116119.469</v>
+        <v>21351.977</v>
       </c>
       <c r="J16">
-        <v>68744.614</v>
+        <v>-1490.537</v>
       </c>
       <c r="K16">
-        <v>163494.324</v>
+        <v>44194.49</v>
       </c>
       <c r="L16">
-        <v>1439747.589</v>
+        <v>47995.855</v>
       </c>
       <c r="M16">
-        <v>844749.856</v>
+        <v>-3555.494</v>
       </c>
       <c r="N16">
-        <v>2034745.322</v>
+        <v>99547.205</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>74.79900000000001</v>
+        <v>14.877</v>
       </c>
       <c r="D17">
-        <v>47.421</v>
+        <v>-0.825</v>
       </c>
       <c r="E17">
-        <v>102.178</v>
+        <v>30.579</v>
       </c>
       <c r="F17">
-        <v>287.244</v>
+        <v>9.736000000000001</v>
       </c>
       <c r="G17">
-        <v>181.849</v>
+        <v>-0.553</v>
       </c>
       <c r="H17">
-        <v>392.639</v>
+        <v>20.026</v>
       </c>
       <c r="I17">
-        <v>3513167.551</v>
+        <v>655871.501</v>
       </c>
       <c r="J17">
-        <v>2227260.468</v>
+        <v>-36379.21</v>
       </c>
       <c r="K17">
-        <v>4799074.635</v>
+        <v>1348122.213</v>
       </c>
       <c r="L17">
-        <v>38203445.769</v>
+        <v>1294944.035</v>
       </c>
       <c r="M17">
-        <v>24185954.095</v>
+        <v>-73503.548</v>
       </c>
       <c r="N17">
-        <v>52220937.442</v>
+        <v>2663391.617</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>372.437</v>
+        <v>71.938</v>
       </c>
       <c r="D18">
-        <v>252.948</v>
+        <v>-2.935</v>
       </c>
       <c r="E18">
-        <v>491.926</v>
+        <v>146.811</v>
       </c>
       <c r="F18">
-        <v>1186.862</v>
+        <v>39.084</v>
       </c>
       <c r="G18">
-        <v>803.999</v>
+        <v>-1.668</v>
       </c>
       <c r="H18">
-        <v>1569.726</v>
+        <v>79.836</v>
       </c>
       <c r="I18">
-        <v>17492623.809</v>
+        <v>3171541.361</v>
       </c>
       <c r="J18">
-        <v>11880463.72</v>
+        <v>-129385.032</v>
       </c>
       <c r="K18">
-        <v>23104783.899</v>
+        <v>6472467.755</v>
       </c>
       <c r="L18">
-        <v>157852707.535</v>
+        <v>5198182.559</v>
       </c>
       <c r="M18">
-        <v>106931862.162</v>
+        <v>-221859.049</v>
       </c>
       <c r="N18">
-        <v>208773552.908</v>
+        <v>10618224.167</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>516.116</v>
+        <v>100.505</v>
       </c>
       <c r="D19">
-        <v>344.582</v>
+        <v>-3.78</v>
       </c>
       <c r="E19">
-        <v>687.649</v>
+        <v>204.789</v>
       </c>
       <c r="F19">
-        <v>1279.172</v>
+        <v>42.415</v>
       </c>
       <c r="G19">
-        <v>851.182</v>
+        <v>-1.655</v>
       </c>
       <c r="H19">
-        <v>1707.161</v>
+        <v>86.485</v>
       </c>
       <c r="I19">
-        <v>24240913.026</v>
+        <v>4430951.072</v>
       </c>
       <c r="J19">
-        <v>16184344.278</v>
+        <v>-166634.972</v>
       </c>
       <c r="K19">
-        <v>32297481.773</v>
+        <v>9028537.116</v>
       </c>
       <c r="L19">
-        <v>170129852.653</v>
+        <v>5641177.851</v>
       </c>
       <c r="M19">
-        <v>113207268.883</v>
+        <v>-220145.907</v>
       </c>
       <c r="N19">
-        <v>227052436.423</v>
+        <v>11502501.609</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>1025.589</v>
+        <v>201.688</v>
       </c>
       <c r="D20">
-        <v>699.665</v>
+        <v>-8.18</v>
       </c>
       <c r="E20">
-        <v>1351.514</v>
+        <v>411.556</v>
       </c>
       <c r="F20">
-        <v>1834.767</v>
+        <v>61.308</v>
       </c>
       <c r="G20">
-        <v>1245.353</v>
+        <v>-2.549</v>
       </c>
       <c r="H20">
-        <v>2424.181</v>
+        <v>125.166</v>
       </c>
       <c r="I20">
-        <v>48169882.636</v>
+        <v>8891802.458000001</v>
       </c>
       <c r="J20">
-        <v>32861849.954</v>
+        <v>-360650.238</v>
       </c>
       <c r="K20">
-        <v>63477915.319</v>
+        <v>18144255.154</v>
       </c>
       <c r="L20">
-        <v>244023997.532</v>
+        <v>8154022.056</v>
       </c>
       <c r="M20">
-        <v>165631946.6</v>
+        <v>-339056.479</v>
       </c>
       <c r="N20">
-        <v>322416048.463</v>
+        <v>16647100.592</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>1270.363</v>
+        <v>252.892</v>
       </c>
       <c r="D21">
-        <v>866.614</v>
+        <v>-9.906000000000001</v>
       </c>
       <c r="E21">
-        <v>1674.111</v>
+        <v>515.689</v>
       </c>
       <c r="F21">
-        <v>1427.605</v>
+        <v>48.352</v>
       </c>
       <c r="G21">
-        <v>975.631</v>
+        <v>-1.86</v>
       </c>
       <c r="H21">
-        <v>1879.58</v>
+        <v>98.56399999999999</v>
       </c>
       <c r="I21">
-        <v>59666388.502</v>
+        <v>11149241.579</v>
       </c>
       <c r="J21">
-        <v>40703137.995</v>
+        <v>-436709.345</v>
       </c>
       <c r="K21">
-        <v>78629639.009</v>
+        <v>22735192.503</v>
       </c>
       <c r="L21">
-        <v>189871496.728</v>
+        <v>6430785.162</v>
       </c>
       <c r="M21">
-        <v>129758861.358</v>
+        <v>-247426.584</v>
       </c>
       <c r="N21">
-        <v>249984132.097</v>
+        <v>13108996.909</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>715.8339999999999</v>
+        <v>139.548</v>
       </c>
       <c r="D22">
-        <v>503.563</v>
+        <v>-2.387</v>
       </c>
       <c r="E22">
-        <v>928.104</v>
+        <v>281.482</v>
       </c>
       <c r="F22">
-        <v>246.107</v>
+        <v>8.259</v>
       </c>
       <c r="G22">
-        <v>167.042</v>
+        <v>-0.249</v>
       </c>
       <c r="H22">
-        <v>325.172</v>
+        <v>16.767</v>
       </c>
       <c r="I22">
-        <v>33621285.815</v>
+        <v>6152243.177</v>
       </c>
       <c r="J22">
-        <v>23651369.772</v>
+        <v>-105216.954</v>
       </c>
       <c r="K22">
-        <v>43591201.859</v>
+        <v>12409703.307</v>
       </c>
       <c r="L22">
-        <v>32732232.572</v>
+        <v>1098415.419</v>
       </c>
       <c r="M22">
-        <v>22216581.039</v>
+        <v>-33157.141</v>
       </c>
       <c r="N22">
-        <v>43247884.105</v>
+        <v>2229987.98</v>
       </c>
     </row>
     <row r="23">
@@ -1455,31 +1455,31 @@
         <v>25.866</v>
       </c>
       <c r="F23">
-        <v>43.585</v>
+        <v>7.258</v>
       </c>
       <c r="G23">
-        <v>-2.159</v>
+        <v>-0.362</v>
       </c>
       <c r="H23">
-        <v>89.328</v>
+        <v>14.877</v>
       </c>
       <c r="I23">
-        <v>187037.127</v>
+        <v>187024.496</v>
       </c>
       <c r="J23">
-        <v>-8948.785</v>
+        <v>-8948.181</v>
       </c>
       <c r="K23">
-        <v>383023.039</v>
+        <v>382997.173</v>
       </c>
       <c r="L23">
-        <v>5796739.272</v>
+        <v>965251.738</v>
       </c>
       <c r="M23">
-        <v>-287187.523</v>
+        <v>-48134.334</v>
       </c>
       <c r="N23">
-        <v>11880666.067</v>
+        <v>1978637.809</v>
       </c>
     </row>
     <row r="24">
@@ -1503,31 +1503,31 @@
         <v>158.169</v>
       </c>
       <c r="F24">
-        <v>236.341</v>
+        <v>39.391</v>
       </c>
       <c r="G24">
-        <v>-9.122</v>
+        <v>-1.51</v>
       </c>
       <c r="H24">
-        <v>481.804</v>
+        <v>80.291</v>
       </c>
       <c r="I24">
-        <v>1149413.238</v>
+        <v>1149335.617</v>
       </c>
       <c r="J24">
-        <v>-43336.396</v>
+        <v>-43333.469</v>
       </c>
       <c r="K24">
-        <v>2342162.872</v>
+        <v>2342004.704</v>
       </c>
       <c r="L24">
-        <v>31433308.11</v>
+        <v>5238987.689</v>
       </c>
       <c r="M24">
-        <v>-1213273.389</v>
+        <v>-200770.125</v>
       </c>
       <c r="N24">
-        <v>64079889.608</v>
+        <v>10678745.504</v>
       </c>
     </row>
     <row r="25">
@@ -1551,31 +1551,31 @@
         <v>512.534</v>
       </c>
       <c r="F25">
-        <v>614.975</v>
+        <v>102.532</v>
       </c>
       <c r="G25">
-        <v>-25.629</v>
+        <v>-4.352</v>
       </c>
       <c r="H25">
-        <v>1255.579</v>
+        <v>209.417</v>
       </c>
       <c r="I25">
-        <v>3715575.019</v>
+        <v>3715324.102</v>
       </c>
       <c r="J25">
-        <v>-158451.105</v>
+        <v>-158440.405</v>
       </c>
       <c r="K25">
-        <v>7589601.144</v>
+        <v>7589088.61</v>
       </c>
       <c r="L25">
-        <v>81791709.858</v>
+        <v>13636804.321</v>
       </c>
       <c r="M25">
-        <v>-3408646.227</v>
+        <v>-578820.7659999999</v>
       </c>
       <c r="N25">
-        <v>166992065.943</v>
+        <v>27852429.408</v>
       </c>
     </row>
     <row r="26">
@@ -1599,31 +1599,31 @@
         <v>839.552</v>
       </c>
       <c r="F26">
-        <v>764.335</v>
+        <v>127.38</v>
       </c>
       <c r="G26">
-        <v>-25.886</v>
+        <v>-4.229</v>
       </c>
       <c r="H26">
-        <v>1554.557</v>
+        <v>258.988</v>
       </c>
       <c r="I26">
-        <v>6114477.376</v>
+        <v>6114064.459</v>
       </c>
       <c r="J26">
-        <v>-203136.865</v>
+        <v>-203123.147</v>
       </c>
       <c r="K26">
-        <v>12432091.617</v>
+        <v>12431252.065</v>
       </c>
       <c r="L26">
-        <v>101656569.665</v>
+        <v>16941474.002</v>
       </c>
       <c r="M26">
-        <v>-3442899.834</v>
+        <v>-562480.5550000001</v>
       </c>
       <c r="N26">
-        <v>206756039.165</v>
+        <v>34445428.56</v>
       </c>
     </row>
     <row r="27">
@@ -1647,31 +1647,31 @@
         <v>2936.602</v>
       </c>
       <c r="F27">
-        <v>1790.768</v>
+        <v>298.527</v>
       </c>
       <c r="G27">
-        <v>-62.046</v>
+        <v>-10.377</v>
       </c>
       <c r="H27">
-        <v>3643.583</v>
+        <v>607.431</v>
       </c>
       <c r="I27">
-        <v>21366918.47</v>
+        <v>21365475.539</v>
       </c>
       <c r="J27">
-        <v>-751364.23</v>
+        <v>-751313.4889999999</v>
       </c>
       <c r="K27">
-        <v>43485201.17</v>
+        <v>43482264.568</v>
       </c>
       <c r="L27">
-        <v>238172193.142</v>
+        <v>39704064.996</v>
       </c>
       <c r="M27">
-        <v>-8252116.859</v>
+        <v>-1380175.963</v>
       </c>
       <c r="N27">
-        <v>484596503.144</v>
+        <v>80788305.955</v>
       </c>
     </row>
     <row r="28">
@@ -1695,31 +1695,31 @@
         <v>3184.187</v>
       </c>
       <c r="F28">
-        <v>1143.612</v>
+        <v>190.521</v>
       </c>
       <c r="G28">
-        <v>-30.005</v>
+        <v>-4.849</v>
       </c>
       <c r="H28">
-        <v>2317.229</v>
+        <v>385.891</v>
       </c>
       <c r="I28">
-        <v>23270337.758</v>
+        <v>23268766.288</v>
       </c>
       <c r="J28">
-        <v>-610769.992</v>
+        <v>-610728.746</v>
       </c>
       <c r="K28">
-        <v>47151445.509</v>
+        <v>47148261.321</v>
       </c>
       <c r="L28">
-        <v>152100388.264</v>
+        <v>25339303.917</v>
       </c>
       <c r="M28">
-        <v>-3990730.387</v>
+        <v>-644961.03</v>
       </c>
       <c r="N28">
-        <v>308191506.915</v>
+        <v>51323568.864</v>
       </c>
     </row>
     <row r="29">
@@ -1743,31 +1743,31 @@
         <v>2283.498</v>
       </c>
       <c r="F29">
-        <v>197.896</v>
+        <v>32.968</v>
       </c>
       <c r="G29">
-        <v>-6.502</v>
+        <v>-1.039</v>
       </c>
       <c r="H29">
-        <v>402.293</v>
+        <v>66.97499999999999</v>
       </c>
       <c r="I29">
-        <v>16746938.941</v>
+        <v>16745808.003</v>
       </c>
       <c r="J29">
-        <v>-320158.194</v>
+        <v>-320136.574</v>
       </c>
       <c r="K29">
-        <v>33814036.077</v>
+        <v>33811752.579</v>
       </c>
       <c r="L29">
-        <v>26320120.41</v>
+        <v>4384735.426</v>
       </c>
       <c r="M29">
-        <v>-864788.198</v>
+        <v>-138156.66</v>
       </c>
       <c r="N29">
-        <v>53505029.018</v>
+        <v>8907627.513</v>
       </c>
     </row>
     <row r="30">
@@ -1791,31 +1791,31 @@
         <v>90.105</v>
       </c>
       <c r="F30">
-        <v>187.338</v>
+        <v>31.654</v>
       </c>
       <c r="G30">
-        <v>-4.729</v>
+        <v>-0.819</v>
       </c>
       <c r="H30">
-        <v>379.405</v>
+        <v>64.128</v>
       </c>
       <c r="I30">
-        <v>1625439.589</v>
+        <v>3347611.396</v>
       </c>
       <c r="J30">
-        <v>-39209.613</v>
+        <v>-80752.64599999999</v>
       </c>
       <c r="K30">
-        <v>3290088.79</v>
+        <v>6775975.437</v>
       </c>
       <c r="L30">
-        <v>24915988.542</v>
+        <v>4210028.586</v>
       </c>
       <c r="M30">
-        <v>-628903.477</v>
+        <v>-108990.679</v>
       </c>
       <c r="N30">
-        <v>50460880.562</v>
+        <v>8529047.851</v>
       </c>
     </row>
     <row r="31">
@@ -1839,31 +1839,31 @@
         <v>277.82</v>
       </c>
       <c r="F31">
-        <v>514.124</v>
+        <v>86.84099999999999</v>
       </c>
       <c r="G31">
-        <v>1.503</v>
+        <v>0.099</v>
       </c>
       <c r="H31">
-        <v>1026.745</v>
+        <v>173.583</v>
       </c>
       <c r="I31">
-        <v>5078759.508</v>
+        <v>10459763.207</v>
       </c>
       <c r="J31">
-        <v>13203.646</v>
+        <v>27193.06</v>
       </c>
       <c r="K31">
-        <v>10144315.37</v>
+        <v>20892333.355</v>
       </c>
       <c r="L31">
-        <v>68378490.119</v>
+        <v>11549834.511</v>
       </c>
       <c r="M31">
-        <v>199844.856</v>
+        <v>13172.062</v>
       </c>
       <c r="N31">
-        <v>136557135.382</v>
+        <v>23086496.96</v>
       </c>
     </row>
     <row r="32">
@@ -1887,31 +1887,31 @@
         <v>833.991</v>
       </c>
       <c r="F32">
-        <v>1221.296</v>
+        <v>206.296</v>
       </c>
       <c r="G32">
-        <v>-10.927</v>
+        <v>-1.79</v>
       </c>
       <c r="H32">
-        <v>2453.519</v>
+        <v>414.382</v>
       </c>
       <c r="I32">
-        <v>15148211.687</v>
+        <v>31197914.966</v>
       </c>
       <c r="J32">
-        <v>-155929.764</v>
+        <v>-321139.13</v>
       </c>
       <c r="K32">
-        <v>30452353.137</v>
+        <v>62716969.061</v>
       </c>
       <c r="L32">
-        <v>162432366.137</v>
+        <v>27437370.461</v>
       </c>
       <c r="M32">
-        <v>-1453263.633</v>
+        <v>-238055.086</v>
       </c>
       <c r="N32">
-        <v>326317995.907</v>
+        <v>55112796.007</v>
       </c>
     </row>
     <row r="33">
@@ -1935,31 +1935,31 @@
         <v>1313.079</v>
       </c>
       <c r="F33">
-        <v>1474.547</v>
+        <v>249.125</v>
       </c>
       <c r="G33">
-        <v>-9.766</v>
+        <v>-1.632</v>
       </c>
       <c r="H33">
-        <v>2958.861</v>
+        <v>499.882</v>
       </c>
       <c r="I33">
-        <v>23897536.472</v>
+        <v>49217249.281</v>
       </c>
       <c r="J33">
-        <v>-150708.827</v>
+        <v>-310386.55</v>
       </c>
       <c r="K33">
-        <v>47945781.771</v>
+        <v>98744885.112</v>
       </c>
       <c r="L33">
-        <v>196114805.099</v>
+        <v>33133622.735</v>
       </c>
       <c r="M33">
-        <v>-1298912.667</v>
+        <v>-217036.637</v>
       </c>
       <c r="N33">
-        <v>393528522.865</v>
+        <v>66484282.106</v>
       </c>
     </row>
     <row r="34">
@@ -1983,31 +1983,31 @@
         <v>4150.928</v>
       </c>
       <c r="F34">
-        <v>3268.487</v>
+        <v>551.905</v>
       </c>
       <c r="G34">
-        <v>63.018</v>
+        <v>10.682</v>
       </c>
       <c r="H34">
-        <v>6473.956</v>
+        <v>1093.129</v>
       </c>
       <c r="I34">
-        <v>76605089.858</v>
+        <v>157769057.415</v>
       </c>
       <c r="J34">
-        <v>1643197.439</v>
+        <v>3384183.891</v>
       </c>
       <c r="K34">
-        <v>151566982.278</v>
+        <v>312153930.938</v>
       </c>
       <c r="L34">
-        <v>434708773.667</v>
+        <v>73403401.03300001</v>
       </c>
       <c r="M34">
-        <v>8381440.632</v>
+        <v>1420708.202</v>
       </c>
       <c r="N34">
-        <v>861036106.7029999</v>
+        <v>145386093.863</v>
       </c>
     </row>
     <row r="35">
@@ -2031,31 +2031,31 @@
         <v>4210.373</v>
       </c>
       <c r="F35">
-        <v>1929.776</v>
+        <v>325.958</v>
       </c>
       <c r="G35">
-        <v>36.907</v>
+        <v>5.98</v>
       </c>
       <c r="H35">
-        <v>3822.646</v>
+        <v>645.936</v>
       </c>
       <c r="I35">
-        <v>77634578.43099999</v>
+        <v>159889300.887</v>
       </c>
       <c r="J35">
-        <v>1531590.862</v>
+        <v>3154328.871</v>
       </c>
       <c r="K35">
-        <v>153737566</v>
+        <v>316624272.903</v>
       </c>
       <c r="L35">
-        <v>256660258.758</v>
+        <v>43352382.882</v>
       </c>
       <c r="M35">
-        <v>4908564.694</v>
+        <v>795307.213</v>
       </c>
       <c r="N35">
-        <v>508411952.822</v>
+        <v>85909458.552</v>
       </c>
     </row>
     <row r="36">
@@ -2079,31 +2079,31 @@
         <v>1751.326</v>
       </c>
       <c r="F36">
-        <v>183</v>
+        <v>30.928</v>
       </c>
       <c r="G36">
-        <v>-3.69</v>
+        <v>-0.66</v>
       </c>
       <c r="H36">
-        <v>369.69</v>
+        <v>62.515</v>
       </c>
       <c r="I36">
-        <v>31916020.461</v>
+        <v>65731408.628</v>
       </c>
       <c r="J36">
-        <v>-115873.992</v>
+        <v>-238643.81</v>
       </c>
       <c r="K36">
-        <v>63947914.913</v>
+        <v>131701461.066</v>
       </c>
       <c r="L36">
-        <v>24339009.57</v>
+        <v>4113398.096</v>
       </c>
       <c r="M36">
-        <v>-490787.395</v>
+        <v>-87718.02099999999</v>
       </c>
       <c r="N36">
-        <v>49168806.535</v>
+        <v>8314514.213</v>
       </c>
     </row>
     <row r="37">
@@ -2223,31 +2223,31 @@
         <v>3.757</v>
       </c>
       <c r="F39">
-        <v>16.436</v>
+        <v>3.737</v>
       </c>
       <c r="G39">
-        <v>9.286</v>
+        <v>2.111</v>
       </c>
       <c r="H39">
-        <v>23.586</v>
+        <v>5.363</v>
       </c>
       <c r="I39">
-        <v>59441.215</v>
+        <v>44000.819</v>
       </c>
       <c r="J39">
-        <v>33406.924</v>
+        <v>24729.172</v>
       </c>
       <c r="K39">
-        <v>85475.50599999999</v>
+        <v>63272.465</v>
       </c>
       <c r="L39">
-        <v>2185998.734</v>
+        <v>497046.131</v>
       </c>
       <c r="M39">
-        <v>1235083.038</v>
+        <v>280820.79</v>
       </c>
       <c r="N39">
-        <v>3136914.43</v>
+        <v>713271.473</v>
       </c>
     </row>
     <row r="40">
@@ -2271,31 +2271,31 @@
         <v>18.963</v>
       </c>
       <c r="F40">
-        <v>67.512</v>
+        <v>15.352</v>
       </c>
       <c r="G40">
-        <v>39.759</v>
+        <v>9.039</v>
       </c>
       <c r="H40">
-        <v>95.265</v>
+        <v>21.665</v>
       </c>
       <c r="I40">
-        <v>305485.354</v>
+        <v>226132.754</v>
       </c>
       <c r="J40">
-        <v>179603.81</v>
+        <v>132950.086</v>
       </c>
       <c r="K40">
-        <v>431366.898</v>
+        <v>319315.421</v>
       </c>
       <c r="L40">
-        <v>8979123.140000001</v>
+        <v>2041853.183</v>
       </c>
       <c r="M40">
-        <v>5287987.397</v>
+        <v>1202246.616</v>
       </c>
       <c r="N40">
-        <v>12670258.883</v>
+        <v>2881459.75</v>
       </c>
     </row>
     <row r="41">
@@ -2319,31 +2319,31 @@
         <v>176.747</v>
       </c>
       <c r="F41">
-        <v>446.506</v>
+        <v>101.527</v>
       </c>
       <c r="G41">
-        <v>269.177</v>
+        <v>61.194</v>
       </c>
       <c r="H41">
-        <v>623.836</v>
+        <v>141.86</v>
       </c>
       <c r="I41">
-        <v>2883721.281</v>
+        <v>2134648.438</v>
       </c>
       <c r="J41">
-        <v>1746807.289</v>
+        <v>1293058.2</v>
       </c>
       <c r="K41">
-        <v>4020635.274</v>
+        <v>2976238.675</v>
       </c>
       <c r="L41">
-        <v>59385342.968</v>
+        <v>13503096.266</v>
       </c>
       <c r="M41">
-        <v>35800547.463</v>
+        <v>8138796.497</v>
       </c>
       <c r="N41">
-        <v>82970138.473</v>
+        <v>18867396.034</v>
       </c>
     </row>
     <row r="42">
@@ -2367,31 +2367,31 @@
         <v>929.276</v>
       </c>
       <c r="F42">
-        <v>1402.664</v>
+        <v>319.004</v>
       </c>
       <c r="G42">
-        <v>846.909</v>
+        <v>192.714</v>
       </c>
       <c r="H42">
-        <v>1958.418</v>
+        <v>445.295</v>
       </c>
       <c r="I42">
-        <v>15153912.544</v>
+        <v>11217545.865</v>
       </c>
       <c r="J42">
-        <v>9168649.772</v>
+        <v>6787009.562</v>
       </c>
       <c r="K42">
-        <v>21139175.316</v>
+        <v>15648082.168</v>
       </c>
       <c r="L42">
-        <v>186554281.796</v>
+        <v>42427575.4</v>
       </c>
       <c r="M42">
-        <v>112638946.385</v>
+        <v>25630953.68</v>
       </c>
       <c r="N42">
-        <v>260469617.206</v>
+        <v>59224197.121</v>
       </c>
     </row>
     <row r="43">
@@ -2415,31 +2415,31 @@
         <v>3844.765</v>
       </c>
       <c r="F43">
-        <v>1553.85</v>
+        <v>353.344</v>
       </c>
       <c r="G43">
-        <v>902.528</v>
+        <v>205.045</v>
       </c>
       <c r="H43">
-        <v>2205.172</v>
+        <v>501.643</v>
       </c>
       <c r="I43">
-        <v>62579536.45</v>
+        <v>46323932.402</v>
       </c>
       <c r="J43">
-        <v>37698357.764</v>
+        <v>27905866.291</v>
       </c>
       <c r="K43">
-        <v>87460715.13600001</v>
+        <v>64741998.513</v>
       </c>
       <c r="L43">
-        <v>206662050.423</v>
+        <v>46994726.683</v>
       </c>
       <c r="M43">
-        <v>120036230.223</v>
+        <v>27270983.159</v>
       </c>
       <c r="N43">
-        <v>293287870.623</v>
+        <v>66718470.207</v>
       </c>
     </row>
     <row r="44">
@@ -2463,13 +2463,13 @@
         <v>22702.549</v>
       </c>
       <c r="F44">
-        <v>28673.854</v>
+        <v>28708.366</v>
       </c>
       <c r="G44">
-        <v>15986.521</v>
+        <v>16072.328</v>
       </c>
       <c r="H44">
-        <v>41361.188</v>
+        <v>41344.404</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>3813622622.23</v>
+        <v>3818212707.109</v>
       </c>
       <c r="M44">
-        <v>2126207261.833</v>
+        <v>2137619683.878</v>
       </c>
       <c r="N44">
-        <v>5501037982.627</v>
+        <v>5498805730.339</v>
       </c>
     </row>
     <row r="45">
@@ -2511,13 +2511,13 @@
         <v>50528.316</v>
       </c>
       <c r="F45">
-        <v>57568.363</v>
+        <v>57532.49</v>
       </c>
       <c r="G45">
-        <v>34365.643</v>
+        <v>34335.921</v>
       </c>
       <c r="H45">
-        <v>80771.083</v>
+        <v>80729.05899999999</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2529,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>7656592248.182</v>
+        <v>7651821166.133</v>
       </c>
       <c r="M45">
-        <v>4570630471.883</v>
+        <v>4566677477.43</v>
       </c>
       <c r="N45">
-        <v>10742554024.48</v>
+        <v>10736964854.835</v>
       </c>
     </row>
     <row r="46">
@@ -2559,13 +2559,13 @@
         <v>59505.237</v>
       </c>
       <c r="F46">
-        <v>54998.934</v>
+        <v>55083.914</v>
       </c>
       <c r="G46">
-        <v>32719.877</v>
+        <v>32727.028</v>
       </c>
       <c r="H46">
-        <v>77277.99099999999</v>
+        <v>77440.799</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7314858212.609</v>
+        <v>7326160536.575</v>
       </c>
       <c r="M46">
-        <v>4351743603.523</v>
+        <v>4352694762.073</v>
       </c>
       <c r="N46">
-        <v>10277972821.694</v>
+        <v>10299626311.078</v>
       </c>
     </row>
     <row r="47">
@@ -2607,13 +2607,13 @@
         <v>34327.633</v>
       </c>
       <c r="F47">
-        <v>24706.464</v>
+        <v>24731.908</v>
       </c>
       <c r="G47">
-        <v>14803.798</v>
+        <v>14810.952</v>
       </c>
       <c r="H47">
-        <v>34609.129</v>
+        <v>34652.863</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>3285959662.204</v>
+        <v>3289343719.639</v>
       </c>
       <c r="M47">
-        <v>1968905154.529</v>
+        <v>1969856629.018</v>
       </c>
       <c r="N47">
-        <v>4603014169.879</v>
+        <v>4608830810.261</v>
       </c>
     </row>
     <row r="48">
@@ -2655,13 +2655,13 @@
         <v>51114.456</v>
       </c>
       <c r="F48">
-        <v>26540.13</v>
+        <v>26549.387</v>
       </c>
       <c r="G48">
-        <v>16264.898</v>
+        <v>16259.624</v>
       </c>
       <c r="H48">
-        <v>36815.362</v>
+        <v>36839.15</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3529837277.452</v>
+        <v>3531068468.286</v>
       </c>
       <c r="M48">
-        <v>2163231414.111</v>
+        <v>2162530014.001</v>
       </c>
       <c r="N48">
-        <v>4896443140.793</v>
+        <v>4899606922.57</v>
       </c>
     </row>
     <row r="49">
@@ -2703,13 +2703,13 @@
         <v>30358.498</v>
       </c>
       <c r="F49">
-        <v>9676.754999999999</v>
+        <v>9665.412</v>
       </c>
       <c r="G49">
-        <v>5960.857</v>
+        <v>5950.846</v>
       </c>
       <c r="H49">
-        <v>13392.654</v>
+        <v>13379.979</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1287008462.761</v>
+        <v>1285499820.982</v>
       </c>
       <c r="M49">
-        <v>792793986.6900001</v>
+        <v>791462462.383</v>
       </c>
       <c r="N49">
-        <v>1781222938.833</v>
+        <v>1779537179.581</v>
       </c>
     </row>
     <row r="50">

--- a/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
@@ -434,26 +434,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C2">
-        <v>105.591</v>
+        <v>448.872</v>
       </c>
       <c r="D2">
-        <v>65.155</v>
+        <v>371.719</v>
       </c>
       <c r="E2">
-        <v>146.027</v>
+        <v>526.026</v>
       </c>
       <c r="F2">
-        <v>1049.331</v>
+        <v>4277.535</v>
       </c>
       <c r="G2">
-        <v>649.484</v>
+        <v>3545.256</v>
       </c>
       <c r="H2">
-        <v>1449.178</v>
+        <v>5009.814</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>139561033.913</v>
+        <v>568912098.75</v>
       </c>
       <c r="M2">
-        <v>86381408.41599999</v>
+        <v>471518988.045</v>
       </c>
       <c r="N2">
-        <v>192740659.409</v>
+        <v>666305209.455</v>
       </c>
     </row>
     <row r="3">
@@ -482,26 +482,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C3">
-        <v>272.83</v>
+        <v>862.5309999999999</v>
       </c>
       <c r="D3">
-        <v>177.042</v>
+        <v>724.717</v>
       </c>
       <c r="E3">
-        <v>368.618</v>
+        <v>1000.346</v>
       </c>
       <c r="F3">
-        <v>2359.401</v>
+        <v>6690.226</v>
       </c>
       <c r="G3">
-        <v>1534.839</v>
+        <v>5628.863</v>
       </c>
       <c r="H3">
-        <v>3183.962</v>
+        <v>7751.589</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>313800270.815</v>
+        <v>889800063.336</v>
       </c>
       <c r="M3">
-        <v>204133555.037</v>
+        <v>748638816.308</v>
       </c>
       <c r="N3">
-        <v>423466986.593</v>
+        <v>1030961310.364</v>
       </c>
     </row>
     <row r="4">
@@ -530,26 +530,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C4">
-        <v>857.726</v>
+        <v>2289.253</v>
       </c>
       <c r="D4">
-        <v>537.0359999999999</v>
+        <v>1928.068</v>
       </c>
       <c r="E4">
-        <v>1178.415</v>
+        <v>2650.437</v>
       </c>
       <c r="F4">
-        <v>5888.532</v>
+        <v>14167.55</v>
       </c>
       <c r="G4">
-        <v>3704.671</v>
+        <v>11942.511</v>
       </c>
       <c r="H4">
-        <v>8072.393</v>
+        <v>16392.589</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>783174750.706</v>
+        <v>1884284127.071</v>
       </c>
       <c r="M4">
-        <v>492721298.67</v>
+        <v>1588353924.628</v>
       </c>
       <c r="N4">
-        <v>1073628202.741</v>
+        <v>2180214329.513</v>
       </c>
     </row>
     <row r="5">
@@ -578,26 +578,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C5">
-        <v>1509.538</v>
+        <v>4889.453</v>
       </c>
       <c r="D5">
-        <v>966.099</v>
+        <v>4124.2</v>
       </c>
       <c r="E5">
-        <v>2052.977</v>
+        <v>5654.706</v>
       </c>
       <c r="F5">
-        <v>7941.196</v>
+        <v>21942.365</v>
       </c>
       <c r="G5">
-        <v>5105.474</v>
+        <v>18545.553</v>
       </c>
       <c r="H5">
-        <v>10776.917</v>
+        <v>25339.178</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1056179047.607</v>
+        <v>2918334587.232</v>
       </c>
       <c r="M5">
-        <v>679028076.607</v>
+        <v>2466558558.969</v>
       </c>
       <c r="N5">
-        <v>1433330018.607</v>
+        <v>3370110615.494</v>
       </c>
     </row>
     <row r="6">
@@ -626,26 +626,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C6">
-        <v>4670.424</v>
+        <v>10430.115</v>
       </c>
       <c r="D6">
-        <v>3140.252</v>
+        <v>8853.171</v>
       </c>
       <c r="E6">
-        <v>6200.597</v>
+        <v>12007.059</v>
       </c>
       <c r="F6">
-        <v>16808.49</v>
+        <v>29708.925</v>
       </c>
       <c r="G6">
-        <v>11276.5</v>
+        <v>25244.044</v>
       </c>
       <c r="H6">
-        <v>22340.48</v>
+        <v>34173.806</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>2235529145.974</v>
+        <v>3951287042.824</v>
       </c>
       <c r="M6">
-        <v>1499774448.719</v>
+        <v>3357457834.245</v>
       </c>
       <c r="N6">
-        <v>2971283843.229</v>
+        <v>4545116251.403</v>
       </c>
     </row>
     <row r="7">
@@ -674,26 +674,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C7">
-        <v>9049.593999999999</v>
+        <v>16763.274</v>
       </c>
       <c r="D7">
-        <v>6066.017</v>
+        <v>14093.866</v>
       </c>
       <c r="E7">
-        <v>12033.17</v>
+        <v>19432.683</v>
       </c>
       <c r="F7">
-        <v>17355.138</v>
+        <v>20719.033</v>
       </c>
       <c r="G7">
-        <v>11673.32</v>
+        <v>17515.616</v>
       </c>
       <c r="H7">
-        <v>23036.956</v>
+        <v>23922.449</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2308233354.624</v>
+        <v>2755631358.734</v>
       </c>
       <c r="M7">
-        <v>1552551624.86</v>
+        <v>2329576975.778</v>
       </c>
       <c r="N7">
-        <v>3063915084.388</v>
+        <v>3181685741.689</v>
       </c>
     </row>
     <row r="8">
@@ -722,26 +722,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C8">
-        <v>21100.752</v>
+        <v>22828.909</v>
       </c>
       <c r="D8">
-        <v>14333.189</v>
+        <v>18808.241</v>
       </c>
       <c r="E8">
-        <v>27868.315</v>
+        <v>26849.578</v>
       </c>
       <c r="F8">
-        <v>6028.28</v>
+        <v>3328.982</v>
       </c>
       <c r="G8">
-        <v>3934.505</v>
+        <v>2630.057</v>
       </c>
       <c r="H8">
-        <v>8122.055</v>
+        <v>4027.906</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>801761274.035</v>
+        <v>442754567.916</v>
       </c>
       <c r="M8">
-        <v>523289191.925</v>
+        <v>349797606.028</v>
       </c>
       <c r="N8">
-        <v>1080233356.145</v>
+        <v>535711529.805</v>
       </c>
     </row>
     <row r="9">
@@ -770,44 +770,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C9">
-        <v>28.865</v>
+        <v>226.531</v>
       </c>
       <c r="D9">
-        <v>14.195</v>
+        <v>139.214</v>
       </c>
       <c r="E9">
-        <v>43.534</v>
+        <v>313.847</v>
       </c>
       <c r="F9">
-        <v>19.291</v>
+        <v>142.563</v>
       </c>
       <c r="G9">
-        <v>9.462999999999999</v>
+        <v>87.54600000000001</v>
       </c>
       <c r="H9">
-        <v>29.118</v>
+        <v>197.58</v>
       </c>
       <c r="I9">
-        <v>1607816.202</v>
+        <v>12618218.994</v>
       </c>
       <c r="J9">
-        <v>790712.28</v>
+        <v>7754512.3</v>
       </c>
       <c r="K9">
-        <v>2424920.125</v>
+        <v>17481925.689</v>
       </c>
       <c r="L9">
-        <v>2565657.509</v>
+        <v>18960899.212</v>
       </c>
       <c r="M9">
-        <v>1258605.375</v>
+        <v>11643619.096</v>
       </c>
       <c r="N9">
-        <v>3872709.642</v>
+        <v>26278179.327</v>
       </c>
     </row>
     <row r="10">
@@ -818,44 +818,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C10">
-        <v>74.398</v>
+        <v>480.966</v>
       </c>
       <c r="D10">
-        <v>38.791</v>
+        <v>299.554</v>
       </c>
       <c r="E10">
-        <v>110.005</v>
+        <v>662.377</v>
       </c>
       <c r="F10">
-        <v>43.205</v>
+        <v>247.562</v>
       </c>
       <c r="G10">
-        <v>22.493</v>
+        <v>154.246</v>
       </c>
       <c r="H10">
-        <v>63.917</v>
+        <v>340.878</v>
       </c>
       <c r="I10">
-        <v>4144100.095</v>
+        <v>26790745.136</v>
       </c>
       <c r="J10">
-        <v>2160715.272</v>
+        <v>16685751.473</v>
       </c>
       <c r="K10">
-        <v>6127484.918</v>
+        <v>36895738.799</v>
       </c>
       <c r="L10">
-        <v>5746247.378</v>
+        <v>32925748.891</v>
       </c>
       <c r="M10">
-        <v>2991582.443</v>
+        <v>20514662.593</v>
       </c>
       <c r="N10">
-        <v>8500912.312999999</v>
+        <v>45336835.19</v>
       </c>
     </row>
     <row r="11">
@@ -866,44 +866,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C11">
-        <v>264.869</v>
+        <v>1559.311</v>
       </c>
       <c r="D11">
-        <v>131.496</v>
+        <v>963.557</v>
       </c>
       <c r="E11">
-        <v>398.242</v>
+        <v>2155.065</v>
       </c>
       <c r="F11">
-        <v>120.929</v>
+        <v>641.12</v>
       </c>
       <c r="G11">
-        <v>60.31</v>
+        <v>396.567</v>
       </c>
       <c r="H11">
-        <v>181.547</v>
+        <v>885.674</v>
       </c>
       <c r="I11">
-        <v>14753753.497</v>
+        <v>86856760.43700001</v>
       </c>
       <c r="J11">
-        <v>7324615.803</v>
+        <v>53672077.549</v>
       </c>
       <c r="K11">
-        <v>22182891.19</v>
+        <v>120041443.325</v>
       </c>
       <c r="L11">
-        <v>16083492.198</v>
+        <v>85269014.647</v>
       </c>
       <c r="M11">
-        <v>8021289.565</v>
+        <v>52743432.632</v>
       </c>
       <c r="N11">
-        <v>24145694.831</v>
+        <v>117794596.662</v>
       </c>
     </row>
     <row r="12">
@@ -914,44 +914,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C12">
-        <v>581.76</v>
+        <v>3894.702</v>
       </c>
       <c r="D12">
-        <v>297.451</v>
+        <v>2427.819</v>
       </c>
       <c r="E12">
-        <v>866.069</v>
+        <v>5361.584</v>
       </c>
       <c r="F12">
-        <v>202.021</v>
+        <v>1153.087</v>
       </c>
       <c r="G12">
-        <v>103.348</v>
+        <v>718.5069999999999</v>
       </c>
       <c r="H12">
-        <v>300.695</v>
+        <v>1587.668</v>
       </c>
       <c r="I12">
-        <v>32405198.574</v>
+        <v>216942678.365</v>
       </c>
       <c r="J12">
-        <v>16568624.094</v>
+        <v>135234387.559</v>
       </c>
       <c r="K12">
-        <v>48241773.054</v>
+        <v>298650969.17</v>
       </c>
       <c r="L12">
-        <v>26868830.494</v>
+        <v>153360627.463</v>
       </c>
       <c r="M12">
-        <v>13745227.084</v>
+        <v>95561390.245</v>
       </c>
       <c r="N12">
-        <v>39992433.904</v>
+        <v>211159864.681</v>
       </c>
     </row>
     <row r="13">
@@ -962,44 +962,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C13">
-        <v>2165.074</v>
+        <v>11141.906</v>
       </c>
       <c r="D13">
-        <v>1189.227</v>
+        <v>7146.459</v>
       </c>
       <c r="E13">
-        <v>3140.92</v>
+        <v>15137.352</v>
       </c>
       <c r="F13">
-        <v>518.202</v>
+        <v>2141.633</v>
       </c>
       <c r="G13">
-        <v>282.861</v>
+        <v>1370.801</v>
       </c>
       <c r="H13">
-        <v>753.544</v>
+        <v>2912.465</v>
       </c>
       <c r="I13">
-        <v>120598942.419</v>
+        <v>620626423.591</v>
       </c>
       <c r="J13">
-        <v>66242342.332</v>
+        <v>398072060.487</v>
       </c>
       <c r="K13">
-        <v>174955542.505</v>
+        <v>843180786.696</v>
       </c>
       <c r="L13">
-        <v>68920889.17200001</v>
+        <v>284837203.788</v>
       </c>
       <c r="M13">
-        <v>37620450.725</v>
+        <v>182316499.749</v>
       </c>
       <c r="N13">
-        <v>100221327.619</v>
+        <v>387357907.827</v>
       </c>
     </row>
     <row r="14">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C14">
-        <v>3664.157</v>
+        <v>13325.084</v>
       </c>
       <c r="D14">
-        <v>2000.445</v>
+        <v>8356.066999999999</v>
       </c>
       <c r="E14">
-        <v>5327.87</v>
+        <v>18294.1</v>
       </c>
       <c r="F14">
-        <v>503.405</v>
+        <v>1264.399</v>
       </c>
       <c r="G14">
-        <v>275.121</v>
+        <v>789.7670000000001</v>
       </c>
       <c r="H14">
-        <v>731.689</v>
+        <v>1739.031</v>
       </c>
       <c r="I14">
-        <v>204100891.041</v>
+        <v>742233812.592</v>
       </c>
       <c r="J14">
-        <v>111428770.49</v>
+        <v>465449665.973</v>
       </c>
       <c r="K14">
-        <v>296773011.592</v>
+        <v>1019017959.21</v>
       </c>
       <c r="L14">
-        <v>66952841.036</v>
+        <v>168165054.828</v>
       </c>
       <c r="M14">
-        <v>36591060.271</v>
+        <v>105038981.666</v>
       </c>
       <c r="N14">
-        <v>97314621.801</v>
+        <v>231291127.99</v>
       </c>
     </row>
     <row r="15">
@@ -1058,44 +1058,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C15">
-        <v>3700.475</v>
+        <v>8717.409</v>
       </c>
       <c r="D15">
-        <v>1943.729</v>
+        <v>5313.009</v>
       </c>
       <c r="E15">
-        <v>5457.221</v>
+        <v>12121.808</v>
       </c>
       <c r="F15">
-        <v>122.625</v>
+        <v>123.008</v>
       </c>
       <c r="G15">
-        <v>60.944</v>
+        <v>70.733</v>
       </c>
       <c r="H15">
-        <v>184.307</v>
+        <v>175.283</v>
       </c>
       <c r="I15">
-        <v>206123861.715</v>
+        <v>485577095.838</v>
       </c>
       <c r="J15">
-        <v>108269594.279</v>
+        <v>295945215.572</v>
       </c>
       <c r="K15">
-        <v>303978129.15</v>
+        <v>675208976.104</v>
       </c>
       <c r="L15">
-        <v>16309185.37</v>
+        <v>16360014.429</v>
       </c>
       <c r="M15">
-        <v>8105531.188</v>
+        <v>9407453.546</v>
       </c>
       <c r="N15">
-        <v>24512839.551</v>
+        <v>23312575.313</v>
       </c>
     </row>
     <row r="16">
@@ -1106,44 +1106,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C16">
-        <v>0.484</v>
+        <v>6.568</v>
       </c>
       <c r="D16">
-        <v>-0.034</v>
+        <v>0.077</v>
       </c>
       <c r="E16">
-        <v>1.002</v>
+        <v>13.058</v>
       </c>
       <c r="F16">
-        <v>0.361</v>
+        <v>4.564</v>
       </c>
       <c r="G16">
-        <v>-0.027</v>
+        <v>0.046</v>
       </c>
       <c r="H16">
-        <v>0.748</v>
+        <v>9.082000000000001</v>
       </c>
       <c r="I16">
-        <v>21351.977</v>
+        <v>289549.633</v>
       </c>
       <c r="J16">
-        <v>-1490.537</v>
+        <v>3412.597</v>
       </c>
       <c r="K16">
-        <v>44194.49</v>
+        <v>575686.6679999999</v>
       </c>
       <c r="L16">
-        <v>47995.855</v>
+        <v>606994.61</v>
       </c>
       <c r="M16">
-        <v>-3555.494</v>
+        <v>6061.979</v>
       </c>
       <c r="N16">
-        <v>99547.205</v>
+        <v>1207927.24</v>
       </c>
     </row>
     <row r="17">
@@ -1154,44 +1154,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C17">
-        <v>14.877</v>
+        <v>61.077</v>
       </c>
       <c r="D17">
-        <v>-0.825</v>
+        <v>1.21</v>
       </c>
       <c r="E17">
-        <v>30.579</v>
+        <v>120.945</v>
       </c>
       <c r="F17">
-        <v>9.736000000000001</v>
+        <v>36.158</v>
       </c>
       <c r="G17">
-        <v>-0.553</v>
+        <v>0.711</v>
       </c>
       <c r="H17">
-        <v>20.026</v>
+        <v>71.60599999999999</v>
       </c>
       <c r="I17">
-        <v>655871.501</v>
+        <v>2692718.651</v>
       </c>
       <c r="J17">
-        <v>-36379.21</v>
+        <v>53334.556</v>
       </c>
       <c r="K17">
-        <v>1348122.213</v>
+        <v>5332102.746</v>
       </c>
       <c r="L17">
-        <v>1294944.035</v>
+        <v>4809048.126</v>
       </c>
       <c r="M17">
-        <v>-73503.548</v>
+        <v>94539.11500000001</v>
       </c>
       <c r="N17">
-        <v>2663391.617</v>
+        <v>9523557.137</v>
       </c>
     </row>
     <row r="18">
@@ -1202,44 +1202,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C18">
-        <v>71.938</v>
+        <v>166.543</v>
       </c>
       <c r="D18">
-        <v>-2.935</v>
+        <v>4.799</v>
       </c>
       <c r="E18">
-        <v>146.811</v>
+        <v>328.287</v>
       </c>
       <c r="F18">
-        <v>39.084</v>
+        <v>81.209</v>
       </c>
       <c r="G18">
-        <v>-1.668</v>
+        <v>2.339</v>
       </c>
       <c r="H18">
-        <v>79.836</v>
+        <v>160.079</v>
       </c>
       <c r="I18">
-        <v>3171541.361</v>
+        <v>7342375.398</v>
       </c>
       <c r="J18">
-        <v>-129385.032</v>
+        <v>211557.015</v>
       </c>
       <c r="K18">
-        <v>6472467.755</v>
+        <v>14473193.782</v>
       </c>
       <c r="L18">
-        <v>5198182.559</v>
+        <v>10800830.363</v>
       </c>
       <c r="M18">
-        <v>-221859.049</v>
+        <v>311105.659</v>
       </c>
       <c r="N18">
-        <v>10618224.167</v>
+        <v>21290555.067</v>
       </c>
     </row>
     <row r="19">
@@ -1250,44 +1250,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C19">
-        <v>100.505</v>
+        <v>253.554</v>
       </c>
       <c r="D19">
-        <v>-3.78</v>
+        <v>7.288</v>
       </c>
       <c r="E19">
-        <v>204.789</v>
+        <v>499.819</v>
       </c>
       <c r="F19">
-        <v>42.415</v>
+        <v>91.69499999999999</v>
       </c>
       <c r="G19">
-        <v>-1.655</v>
+        <v>2.656</v>
       </c>
       <c r="H19">
-        <v>86.485</v>
+        <v>180.735</v>
       </c>
       <c r="I19">
-        <v>4430951.072</v>
+        <v>11178419.656</v>
       </c>
       <c r="J19">
-        <v>-166634.972</v>
+        <v>321300.031</v>
       </c>
       <c r="K19">
-        <v>9028537.116</v>
+        <v>22035539.28</v>
       </c>
       <c r="L19">
-        <v>5641177.851</v>
+        <v>12195441.177</v>
       </c>
       <c r="M19">
-        <v>-220145.907</v>
+        <v>353190.14</v>
       </c>
       <c r="N19">
-        <v>11502501.609</v>
+        <v>24037692.214</v>
       </c>
     </row>
     <row r="20">
@@ -1298,44 +1298,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C20">
-        <v>201.688</v>
+        <v>369.127</v>
       </c>
       <c r="D20">
-        <v>-8.18</v>
+        <v>8.795999999999999</v>
       </c>
       <c r="E20">
-        <v>411.556</v>
+        <v>729.4589999999999</v>
       </c>
       <c r="F20">
-        <v>61.308</v>
+        <v>92.982</v>
       </c>
       <c r="G20">
-        <v>-2.549</v>
+        <v>2.191</v>
       </c>
       <c r="H20">
-        <v>125.166</v>
+        <v>183.773</v>
       </c>
       <c r="I20">
-        <v>8891802.458000001</v>
+        <v>16273723.665</v>
       </c>
       <c r="J20">
-        <v>-360650.238</v>
+        <v>387783.223</v>
       </c>
       <c r="K20">
-        <v>18144255.154</v>
+        <v>32159664.108</v>
       </c>
       <c r="L20">
-        <v>8154022.056</v>
+        <v>12366610.157</v>
       </c>
       <c r="M20">
-        <v>-339056.479</v>
+        <v>291416.587</v>
       </c>
       <c r="N20">
-        <v>16647100.592</v>
+        <v>24441803.728</v>
       </c>
     </row>
     <row r="21">
@@ -1346,44 +1346,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C21">
-        <v>252.892</v>
+        <v>274.844</v>
       </c>
       <c r="D21">
-        <v>-9.906000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="E21">
-        <v>515.689</v>
+        <v>541.379</v>
       </c>
       <c r="F21">
-        <v>48.352</v>
+        <v>39.948</v>
       </c>
       <c r="G21">
-        <v>-1.86</v>
+        <v>1.048</v>
       </c>
       <c r="H21">
-        <v>98.56399999999999</v>
+        <v>78.848</v>
       </c>
       <c r="I21">
-        <v>11149241.579</v>
+        <v>12117066.487</v>
       </c>
       <c r="J21">
-        <v>-436709.345</v>
+        <v>366344.003</v>
       </c>
       <c r="K21">
-        <v>22735192.503</v>
+        <v>23867788.97</v>
       </c>
       <c r="L21">
-        <v>6430785.162</v>
+        <v>5313064.385</v>
       </c>
       <c r="M21">
-        <v>-247426.584</v>
+        <v>139324.422</v>
       </c>
       <c r="N21">
-        <v>13108996.909</v>
+        <v>10486804.348</v>
       </c>
     </row>
     <row r="22">
@@ -1394,44 +1394,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C22">
-        <v>139.548</v>
+        <v>124.568</v>
       </c>
       <c r="D22">
-        <v>-2.387</v>
+        <v>4.261</v>
       </c>
       <c r="E22">
-        <v>281.482</v>
+        <v>244.874</v>
       </c>
       <c r="F22">
-        <v>8.259</v>
+        <v>3.638</v>
       </c>
       <c r="G22">
-        <v>-0.249</v>
+        <v>0.08</v>
       </c>
       <c r="H22">
-        <v>16.767</v>
+        <v>7.195</v>
       </c>
       <c r="I22">
-        <v>6152243.177</v>
+        <v>5491819.223</v>
       </c>
       <c r="J22">
-        <v>-105216.954</v>
+        <v>187862.982</v>
       </c>
       <c r="K22">
-        <v>12409703.307</v>
+        <v>10795775.465</v>
       </c>
       <c r="L22">
-        <v>1098415.419</v>
+        <v>483843.021</v>
       </c>
       <c r="M22">
-        <v>-33157.141</v>
+        <v>10687.903</v>
       </c>
       <c r="N22">
-        <v>2229987.98</v>
+        <v>956998.138</v>
       </c>
     </row>
     <row r="23">
@@ -1442,44 +1442,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C23">
-        <v>12.631</v>
+        <v>1893.67</v>
       </c>
       <c r="D23">
-        <v>-0.604</v>
+        <v>54.01</v>
       </c>
       <c r="E23">
-        <v>25.866</v>
+        <v>3733.33</v>
       </c>
       <c r="F23">
-        <v>7.258</v>
+        <v>1059.163</v>
       </c>
       <c r="G23">
-        <v>-0.362</v>
+        <v>29.842</v>
       </c>
       <c r="H23">
-        <v>14.877</v>
+        <v>2088.485</v>
       </c>
       <c r="I23">
-        <v>187024.496</v>
+        <v>28039571.992</v>
       </c>
       <c r="J23">
-        <v>-8948.181</v>
+        <v>799733.057</v>
       </c>
       <c r="K23">
-        <v>382997.173</v>
+        <v>55279410.927</v>
       </c>
       <c r="L23">
-        <v>965251.738</v>
+        <v>140868732.655</v>
       </c>
       <c r="M23">
-        <v>-48134.334</v>
+        <v>3969000.533</v>
       </c>
       <c r="N23">
-        <v>1978637.809</v>
+        <v>277768464.777</v>
       </c>
     </row>
     <row r="24">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C24">
-        <v>77.621</v>
+        <v>3254.42</v>
       </c>
       <c r="D24">
-        <v>-2.927</v>
+        <v>84.518</v>
       </c>
       <c r="E24">
-        <v>158.169</v>
+        <v>6424.321</v>
       </c>
       <c r="F24">
-        <v>39.391</v>
+        <v>1526.469</v>
       </c>
       <c r="G24">
-        <v>-1.51</v>
+        <v>38.432</v>
       </c>
       <c r="H24">
-        <v>80.291</v>
+        <v>3014.506</v>
       </c>
       <c r="I24">
-        <v>1149335.617</v>
+        <v>48188190.142</v>
       </c>
       <c r="J24">
-        <v>-43333.469</v>
+        <v>1251457.002</v>
       </c>
       <c r="K24">
-        <v>2342004.704</v>
+        <v>95124923.28300001</v>
       </c>
       <c r="L24">
-        <v>5238987.689</v>
+        <v>203020424.026</v>
       </c>
       <c r="M24">
-        <v>-200770.125</v>
+        <v>5111485.68</v>
       </c>
       <c r="N24">
-        <v>10678745.504</v>
+        <v>400929362.373</v>
       </c>
     </row>
     <row r="25">
@@ -1538,44 +1538,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C25">
-        <v>250.917</v>
+        <v>4226.107</v>
       </c>
       <c r="D25">
-        <v>-10.7</v>
+        <v>141.743</v>
       </c>
       <c r="E25">
-        <v>512.534</v>
+        <v>8310.471</v>
       </c>
       <c r="F25">
-        <v>102.532</v>
+        <v>1599.745</v>
       </c>
       <c r="G25">
-        <v>-4.352</v>
+        <v>51.691</v>
       </c>
       <c r="H25">
-        <v>209.417</v>
+        <v>3147.799</v>
       </c>
       <c r="I25">
-        <v>3715324.102</v>
+        <v>62575965.453</v>
       </c>
       <c r="J25">
-        <v>-158440.405</v>
+        <v>2098787.849</v>
       </c>
       <c r="K25">
-        <v>7589088.61</v>
+        <v>123053143.057</v>
       </c>
       <c r="L25">
-        <v>13636804.321</v>
+        <v>212766022.92</v>
       </c>
       <c r="M25">
-        <v>-578820.7659999999</v>
+        <v>6874843.057</v>
       </c>
       <c r="N25">
-        <v>27852429.408</v>
+        <v>418657202.784</v>
       </c>
     </row>
     <row r="26">
@@ -1586,44 +1586,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C26">
-        <v>412.917</v>
+        <v>5650.43</v>
       </c>
       <c r="D26">
-        <v>-13.718</v>
+        <v>181.535</v>
       </c>
       <c r="E26">
-        <v>839.552</v>
+        <v>11119.325</v>
       </c>
       <c r="F26">
-        <v>127.38</v>
+        <v>1535.848</v>
       </c>
       <c r="G26">
-        <v>-4.229</v>
+        <v>50.468</v>
       </c>
       <c r="H26">
-        <v>258.988</v>
+        <v>3021.229</v>
       </c>
       <c r="I26">
-        <v>6114064.459</v>
+        <v>83665914.92900001</v>
       </c>
       <c r="J26">
-        <v>-203123.147</v>
+        <v>2687989.398</v>
       </c>
       <c r="K26">
-        <v>12431252.065</v>
+        <v>164643840.459</v>
       </c>
       <c r="L26">
-        <v>16941474.002</v>
+        <v>204267808.457</v>
       </c>
       <c r="M26">
-        <v>-562480.5550000001</v>
+        <v>6712221.779</v>
       </c>
       <c r="N26">
-        <v>34445428.56</v>
+        <v>401823395.136</v>
       </c>
     </row>
     <row r="27">
@@ -1634,44 +1634,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C27">
-        <v>1442.931</v>
+        <v>8144.413</v>
       </c>
       <c r="D27">
-        <v>-50.74</v>
+        <v>198.11</v>
       </c>
       <c r="E27">
-        <v>2936.602</v>
+        <v>16090.717</v>
       </c>
       <c r="F27">
-        <v>298.527</v>
+        <v>1442.859</v>
       </c>
       <c r="G27">
-        <v>-10.377</v>
+        <v>35.141</v>
       </c>
       <c r="H27">
-        <v>607.431</v>
+        <v>2850.576</v>
       </c>
       <c r="I27">
-        <v>21365475.539</v>
+        <v>120594325.817</v>
       </c>
       <c r="J27">
-        <v>-751313.4889999999</v>
+        <v>2933410.333</v>
       </c>
       <c r="K27">
-        <v>43482264.568</v>
+        <v>238255241.301</v>
       </c>
       <c r="L27">
-        <v>39704064.996</v>
+        <v>191900182.968</v>
       </c>
       <c r="M27">
-        <v>-1380175.963</v>
+        <v>4673814.575</v>
       </c>
       <c r="N27">
-        <v>80788305.955</v>
+        <v>379126551.36</v>
       </c>
     </row>
     <row r="28">
@@ -1682,44 +1682,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C28">
-        <v>1571.471</v>
+        <v>5393.558</v>
       </c>
       <c r="D28">
-        <v>-41.246</v>
+        <v>165.121</v>
       </c>
       <c r="E28">
-        <v>3184.187</v>
+        <v>10621.995</v>
       </c>
       <c r="F28">
-        <v>190.521</v>
+        <v>455.797</v>
       </c>
       <c r="G28">
-        <v>-4.849</v>
+        <v>13.969</v>
       </c>
       <c r="H28">
-        <v>385.891</v>
+        <v>897.625</v>
       </c>
       <c r="I28">
-        <v>23268766.288</v>
+        <v>79862412.934</v>
       </c>
       <c r="J28">
-        <v>-610728.746</v>
+        <v>2444946.704</v>
       </c>
       <c r="K28">
-        <v>47148261.321</v>
+        <v>157279879.164</v>
       </c>
       <c r="L28">
-        <v>25339303.917</v>
+        <v>60620993.733</v>
       </c>
       <c r="M28">
-        <v>-644961.03</v>
+        <v>1857857.621</v>
       </c>
       <c r="N28">
-        <v>51323568.864</v>
+        <v>119384129.845</v>
       </c>
     </row>
     <row r="29">
@@ -1730,44 +1730,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C29">
-        <v>1130.939</v>
+        <v>2151.537</v>
       </c>
       <c r="D29">
-        <v>-21.621</v>
+        <v>67.039</v>
       </c>
       <c r="E29">
-        <v>2283.498</v>
+        <v>4236.035</v>
       </c>
       <c r="F29">
-        <v>32.968</v>
+        <v>24.63</v>
       </c>
       <c r="G29">
-        <v>-1.039</v>
+        <v>0.556</v>
       </c>
       <c r="H29">
-        <v>66.97499999999999</v>
+        <v>48.704</v>
       </c>
       <c r="I29">
-        <v>16745808.003</v>
+        <v>31857809.569</v>
       </c>
       <c r="J29">
-        <v>-320136.574</v>
+        <v>992652.314</v>
       </c>
       <c r="K29">
-        <v>33811752.579</v>
+        <v>62722966.824</v>
       </c>
       <c r="L29">
-        <v>4384735.426</v>
+        <v>3275776.693</v>
       </c>
       <c r="M29">
-        <v>-138156.66</v>
+        <v>73906.535</v>
       </c>
       <c r="N29">
-        <v>8907627.513</v>
+        <v>6477646.851</v>
       </c>
     </row>
     <row r="30">
@@ -1778,44 +1778,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C30">
-        <v>44.516</v>
+        <v>393.539</v>
       </c>
       <c r="D30">
-        <v>-1.074</v>
+        <v>14.379</v>
       </c>
       <c r="E30">
-        <v>90.105</v>
+        <v>772.699</v>
       </c>
       <c r="F30">
-        <v>31.654</v>
+        <v>263.924</v>
       </c>
       <c r="G30">
-        <v>-0.819</v>
+        <v>9.448</v>
       </c>
       <c r="H30">
-        <v>64.128</v>
+        <v>518.4</v>
       </c>
       <c r="I30">
-        <v>3347611.396</v>
+        <v>29594509.504</v>
       </c>
       <c r="J30">
-        <v>-80752.64599999999</v>
+        <v>1081285.756</v>
       </c>
       <c r="K30">
-        <v>6775975.437</v>
+        <v>58107733.253</v>
       </c>
       <c r="L30">
-        <v>4210028.586</v>
+        <v>35101930.436</v>
       </c>
       <c r="M30">
-        <v>-108990.679</v>
+        <v>1256627.863</v>
       </c>
       <c r="N30">
-        <v>8529047.851</v>
+        <v>68947233.01000001</v>
       </c>
     </row>
     <row r="31">
@@ -1826,44 +1826,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C31">
-        <v>139.091</v>
+        <v>639.231</v>
       </c>
       <c r="D31">
-        <v>0.362</v>
+        <v>23.927</v>
       </c>
       <c r="E31">
-        <v>277.82</v>
+        <v>1254.536</v>
       </c>
       <c r="F31">
-        <v>86.84099999999999</v>
+        <v>352.164</v>
       </c>
       <c r="G31">
-        <v>0.099</v>
+        <v>13.485</v>
       </c>
       <c r="H31">
-        <v>173.583</v>
+        <v>690.843</v>
       </c>
       <c r="I31">
-        <v>10459763.207</v>
+        <v>48070821.225</v>
       </c>
       <c r="J31">
-        <v>27193.06</v>
+        <v>1799318.2</v>
       </c>
       <c r="K31">
-        <v>20892333.355</v>
+        <v>94342324.251</v>
       </c>
       <c r="L31">
-        <v>11549834.511</v>
+        <v>46837791.091</v>
       </c>
       <c r="M31">
-        <v>13172.062</v>
+        <v>1793502.857</v>
       </c>
       <c r="N31">
-        <v>23086496.96</v>
+        <v>91882079.32600001</v>
       </c>
     </row>
     <row r="32">
@@ -1874,44 +1874,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C32">
-        <v>414.86</v>
+        <v>933.4589999999999</v>
       </c>
       <c r="D32">
-        <v>-4.27</v>
+        <v>30.49</v>
       </c>
       <c r="E32">
-        <v>833.991</v>
+        <v>1836.427</v>
       </c>
       <c r="F32">
-        <v>206.296</v>
+        <v>410.978</v>
       </c>
       <c r="G32">
-        <v>-1.79</v>
+        <v>13.805</v>
       </c>
       <c r="H32">
-        <v>414.382</v>
+        <v>808.151</v>
       </c>
       <c r="I32">
-        <v>31197914.966</v>
+        <v>70197021.634</v>
       </c>
       <c r="J32">
-        <v>-321139.13</v>
+        <v>2292864.732</v>
       </c>
       <c r="K32">
-        <v>62716969.061</v>
+        <v>138101178.535</v>
       </c>
       <c r="L32">
-        <v>27437370.461</v>
+        <v>54660115.408</v>
       </c>
       <c r="M32">
-        <v>-238055.086</v>
+        <v>1836082.406</v>
       </c>
       <c r="N32">
-        <v>55112796.007</v>
+        <v>107484148.41</v>
       </c>
     </row>
     <row r="33">
@@ -1922,44 +1922,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C33">
-        <v>654.476</v>
+        <v>1531.21</v>
       </c>
       <c r="D33">
-        <v>-4.127</v>
+        <v>63.037</v>
       </c>
       <c r="E33">
-        <v>1313.079</v>
+        <v>2999.384</v>
       </c>
       <c r="F33">
-        <v>249.125</v>
+        <v>487.974</v>
       </c>
       <c r="G33">
-        <v>-1.632</v>
+        <v>20.235</v>
       </c>
       <c r="H33">
-        <v>499.882</v>
+        <v>955.7140000000001</v>
       </c>
       <c r="I33">
-        <v>49217249.281</v>
+        <v>115148551.285</v>
       </c>
       <c r="J33">
-        <v>-310386.55</v>
+        <v>4740427.401</v>
       </c>
       <c r="K33">
-        <v>98744885.112</v>
+        <v>225556675.169</v>
       </c>
       <c r="L33">
-        <v>33133622.735</v>
+        <v>64900554.932</v>
       </c>
       <c r="M33">
-        <v>-217036.637</v>
+        <v>2691203.845</v>
       </c>
       <c r="N33">
-        <v>66484282.106</v>
+        <v>127109906.019</v>
       </c>
     </row>
     <row r="34">
@@ -1970,44 +1970,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C34">
-        <v>2097.965</v>
+        <v>2161.861</v>
       </c>
       <c r="D34">
-        <v>45.002</v>
+        <v>119.03</v>
       </c>
       <c r="E34">
-        <v>4150.928</v>
+        <v>4204.693</v>
       </c>
       <c r="F34">
-        <v>551.905</v>
+        <v>470.348</v>
       </c>
       <c r="G34">
-        <v>10.682</v>
+        <v>25.387</v>
       </c>
       <c r="H34">
-        <v>1093.129</v>
+        <v>915.309</v>
       </c>
       <c r="I34">
-        <v>157769057.415</v>
+        <v>162574130.825</v>
       </c>
       <c r="J34">
-        <v>3384183.891</v>
+        <v>8951152.227</v>
       </c>
       <c r="K34">
-        <v>312153930.938</v>
+        <v>316197109.423</v>
       </c>
       <c r="L34">
-        <v>73403401.03300001</v>
+        <v>62556260.732</v>
       </c>
       <c r="M34">
-        <v>1420708.202</v>
+        <v>3376481.394</v>
       </c>
       <c r="N34">
-        <v>145386093.863</v>
+        <v>121736040.07</v>
       </c>
     </row>
     <row r="35">
@@ -2018,44 +2018,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C35">
-        <v>2126.159</v>
+        <v>689.669</v>
       </c>
       <c r="D35">
-        <v>41.945</v>
+        <v>30.603</v>
       </c>
       <c r="E35">
-        <v>4210.373</v>
+        <v>1348.736</v>
       </c>
       <c r="F35">
-        <v>325.958</v>
+        <v>83.532</v>
       </c>
       <c r="G35">
-        <v>5.98</v>
+        <v>3.596</v>
       </c>
       <c r="H35">
-        <v>645.936</v>
+        <v>163.468</v>
       </c>
       <c r="I35">
-        <v>159889300.887</v>
+        <v>51863836.011</v>
       </c>
       <c r="J35">
-        <v>3154328.871</v>
+        <v>2301338.697</v>
       </c>
       <c r="K35">
-        <v>316624272.903</v>
+        <v>101426333.324</v>
       </c>
       <c r="L35">
-        <v>43352382.882</v>
+        <v>11109792.267</v>
       </c>
       <c r="M35">
-        <v>795307.213</v>
+        <v>478312.001</v>
       </c>
       <c r="N35">
-        <v>85909458.552</v>
+        <v>21741272.534</v>
       </c>
     </row>
     <row r="36">
@@ -2066,44 +2066,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C36">
-        <v>874.076</v>
+        <v>28.229</v>
       </c>
       <c r="D36">
-        <v>-3.173</v>
+        <v>0.746</v>
       </c>
       <c r="E36">
-        <v>1751.326</v>
+        <v>55.711</v>
       </c>
       <c r="F36">
-        <v>30.928</v>
+        <v>0.619</v>
       </c>
       <c r="G36">
-        <v>-0.66</v>
+        <v>0.005</v>
       </c>
       <c r="H36">
-        <v>62.515</v>
+        <v>1.234</v>
       </c>
       <c r="I36">
-        <v>65731408.628</v>
+        <v>2122836.653</v>
       </c>
       <c r="J36">
-        <v>-238643.81</v>
+        <v>56114.641</v>
       </c>
       <c r="K36">
-        <v>131701461.066</v>
+        <v>4189558.665</v>
       </c>
       <c r="L36">
-        <v>4113398.096</v>
+        <v>82376.85799999999</v>
       </c>
       <c r="M36">
-        <v>-87718.02099999999</v>
+        <v>669.797</v>
       </c>
       <c r="N36">
-        <v>8314514.213</v>
+        <v>164083.919</v>
       </c>
     </row>
     <row r="37">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C37">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C38">
@@ -2210,44 +2210,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C39">
-        <v>2.613</v>
+        <v>141.818</v>
       </c>
       <c r="D39">
-        <v>1.469</v>
+        <v>103.498</v>
       </c>
       <c r="E39">
-        <v>3.757</v>
+        <v>180.138</v>
       </c>
       <c r="F39">
-        <v>3.737</v>
+        <v>186.677</v>
       </c>
       <c r="G39">
-        <v>2.111</v>
+        <v>136.181</v>
       </c>
       <c r="H39">
-        <v>5.363</v>
+        <v>237.173</v>
       </c>
       <c r="I39">
-        <v>44000.819</v>
+        <v>2388071.387</v>
       </c>
       <c r="J39">
-        <v>24729.172</v>
+        <v>1742802.269</v>
       </c>
       <c r="K39">
-        <v>63272.465</v>
+        <v>3033340.506</v>
       </c>
       <c r="L39">
-        <v>497046.131</v>
+        <v>24828021.818</v>
       </c>
       <c r="M39">
-        <v>280820.79</v>
+        <v>18112028.585</v>
       </c>
       <c r="N39">
-        <v>713271.473</v>
+        <v>31544015.051</v>
       </c>
     </row>
     <row r="40">
@@ -2258,44 +2258,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C40">
-        <v>13.429</v>
+        <v>314.77</v>
       </c>
       <c r="D40">
-        <v>7.895</v>
+        <v>229.795</v>
       </c>
       <c r="E40">
-        <v>18.963</v>
+        <v>399.745</v>
       </c>
       <c r="F40">
-        <v>15.352</v>
+        <v>308.696</v>
       </c>
       <c r="G40">
-        <v>9.039</v>
+        <v>225.191</v>
       </c>
       <c r="H40">
-        <v>21.665</v>
+        <v>392.202</v>
       </c>
       <c r="I40">
-        <v>226132.754</v>
+        <v>5300411.263</v>
       </c>
       <c r="J40">
-        <v>132950.086</v>
+        <v>3869515.879</v>
       </c>
       <c r="K40">
-        <v>319315.421</v>
+        <v>6731306.647</v>
       </c>
       <c r="L40">
-        <v>2041853.183</v>
+        <v>41056584.651</v>
       </c>
       <c r="M40">
-        <v>1202246.616</v>
+        <v>29950347.074</v>
       </c>
       <c r="N40">
-        <v>2881459.75</v>
+        <v>52162822.227</v>
       </c>
     </row>
     <row r="41">
@@ -2306,44 +2306,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C41">
-        <v>126.768</v>
+        <v>1746.884</v>
       </c>
       <c r="D41">
-        <v>76.789</v>
+        <v>1285.847</v>
       </c>
       <c r="E41">
-        <v>176.747</v>
+        <v>2207.921</v>
       </c>
       <c r="F41">
-        <v>101.527</v>
+        <v>1078.871</v>
       </c>
       <c r="G41">
-        <v>61.194</v>
+        <v>793.683</v>
       </c>
       <c r="H41">
-        <v>141.86</v>
+        <v>1364.06</v>
       </c>
       <c r="I41">
-        <v>2134648.438</v>
+        <v>29415776.364</v>
       </c>
       <c r="J41">
-        <v>1293058.2</v>
+        <v>21652372.327</v>
       </c>
       <c r="K41">
-        <v>2976238.675</v>
+        <v>37179180.4</v>
       </c>
       <c r="L41">
-        <v>13503096.266</v>
+        <v>143489868.587</v>
       </c>
       <c r="M41">
-        <v>8138796.497</v>
+        <v>105559813.708</v>
       </c>
       <c r="N41">
-        <v>18867396.034</v>
+        <v>181419923.467</v>
       </c>
     </row>
     <row r="42">
@@ -2354,44 +2354,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C42">
-        <v>666.165</v>
+        <v>5026.901</v>
       </c>
       <c r="D42">
-        <v>403.053</v>
+        <v>3670.677</v>
       </c>
       <c r="E42">
-        <v>929.276</v>
+        <v>6383.125</v>
       </c>
       <c r="F42">
-        <v>319.004</v>
+        <v>1550.71</v>
       </c>
       <c r="G42">
-        <v>192.714</v>
+        <v>1129.844</v>
       </c>
       <c r="H42">
-        <v>445.295</v>
+        <v>1971.577</v>
       </c>
       <c r="I42">
-        <v>11217545.865</v>
+        <v>84647985.89399999</v>
       </c>
       <c r="J42">
-        <v>6787009.562</v>
+        <v>61810522.29</v>
       </c>
       <c r="K42">
-        <v>15648082.168</v>
+        <v>107485449.498</v>
       </c>
       <c r="L42">
-        <v>42427575.4</v>
+        <v>206244472.576</v>
       </c>
       <c r="M42">
-        <v>25630953.68</v>
+        <v>150269218.668</v>
       </c>
       <c r="N42">
-        <v>59224197.121</v>
+        <v>262219726.483</v>
       </c>
     </row>
     <row r="43">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C43">
-        <v>2750.991</v>
+        <v>6174.745</v>
       </c>
       <c r="D43">
-        <v>1657.216</v>
+        <v>4422.135</v>
       </c>
       <c r="E43">
-        <v>3844.765</v>
+        <v>7927.355</v>
       </c>
       <c r="F43">
-        <v>353.344</v>
+        <v>306.792</v>
       </c>
       <c r="G43">
-        <v>205.045</v>
+        <v>209.592</v>
       </c>
       <c r="H43">
-        <v>501.643</v>
+        <v>403.993</v>
       </c>
       <c r="I43">
-        <v>46323932.402</v>
+        <v>103976530.028</v>
       </c>
       <c r="J43">
-        <v>27905866.291</v>
+        <v>74464325.168</v>
       </c>
       <c r="K43">
-        <v>64741998.513</v>
+        <v>133488734.888</v>
       </c>
       <c r="L43">
-        <v>46994726.683</v>
+        <v>40803386.096</v>
       </c>
       <c r="M43">
-        <v>27270983.159</v>
+        <v>27875711.287</v>
       </c>
       <c r="N43">
-        <v>66718470.207</v>
+        <v>53731060.905</v>
       </c>
     </row>
     <row r="44">
@@ -2450,26 +2450,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C44">
-        <v>15844.279</v>
+        <v>23404.286</v>
       </c>
       <c r="D44">
-        <v>8986.009</v>
+        <v>17200.907</v>
       </c>
       <c r="E44">
-        <v>22702.549</v>
+        <v>29607.665</v>
       </c>
       <c r="F44">
-        <v>28708.366</v>
+        <v>40737.83</v>
       </c>
       <c r="G44">
-        <v>16072.328</v>
+        <v>29788.922</v>
       </c>
       <c r="H44">
-        <v>41344.404</v>
+        <v>51686.737</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>3818212707.109</v>
+        <v>5418131360.702</v>
       </c>
       <c r="M44">
-        <v>2137619683.878</v>
+        <v>3961926648.764</v>
       </c>
       <c r="N44">
-        <v>5498805730.339</v>
+        <v>6874336072.64</v>
       </c>
     </row>
     <row r="45">
@@ -2498,26 +2498,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C45">
-        <v>36136.827</v>
+        <v>25167.979</v>
       </c>
       <c r="D45">
-        <v>21745.339</v>
+        <v>18613.18</v>
       </c>
       <c r="E45">
-        <v>50528.316</v>
+        <v>31722.777</v>
       </c>
       <c r="F45">
-        <v>57532.49</v>
+        <v>36597.704</v>
       </c>
       <c r="G45">
-        <v>34335.921</v>
+        <v>26926.396</v>
       </c>
       <c r="H45">
-        <v>80729.05899999999</v>
+        <v>46269.013</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2529,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>7651821166.133</v>
+        <v>4867494659.078</v>
       </c>
       <c r="M45">
-        <v>4566677477.43</v>
+        <v>3581210651.977</v>
       </c>
       <c r="N45">
-        <v>10736964854.835</v>
+        <v>6153778666.179</v>
       </c>
     </row>
     <row r="46">
@@ -2546,26 +2546,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C46">
-        <v>42366.258</v>
+        <v>24143.745</v>
       </c>
       <c r="D46">
-        <v>25227.278</v>
+        <v>17870.784</v>
       </c>
       <c r="E46">
-        <v>59505.237</v>
+        <v>30416.705</v>
       </c>
       <c r="F46">
-        <v>55083.914</v>
+        <v>28323.726</v>
       </c>
       <c r="G46">
-        <v>32727.028</v>
+        <v>20837.751</v>
       </c>
       <c r="H46">
-        <v>77440.799</v>
+        <v>35809.701</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7326160536.575</v>
+        <v>3767055556.298</v>
       </c>
       <c r="M46">
-        <v>4352694762.073</v>
+        <v>2771420924.548</v>
       </c>
       <c r="N46">
-        <v>10299626311.078</v>
+        <v>4762690188.049</v>
       </c>
     </row>
     <row r="47">
@@ -2594,26 +2594,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C47">
-        <v>24558.021</v>
+        <v>23301.198</v>
       </c>
       <c r="D47">
-        <v>14788.41</v>
+        <v>17346.353</v>
       </c>
       <c r="E47">
-        <v>34327.633</v>
+        <v>29256.043</v>
       </c>
       <c r="F47">
-        <v>24731.908</v>
+        <v>19982.586</v>
       </c>
       <c r="G47">
-        <v>14810.952</v>
+        <v>14790.738</v>
       </c>
       <c r="H47">
-        <v>34652.863</v>
+        <v>25174.435</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>3289343719.639</v>
+        <v>2657683982.743</v>
       </c>
       <c r="M47">
-        <v>1969856629.018</v>
+        <v>1967168132.255</v>
       </c>
       <c r="N47">
-        <v>4608830810.261</v>
+        <v>3348199833.231</v>
       </c>
     </row>
     <row r="48">
@@ -2642,26 +2642,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C48">
-        <v>36998.691</v>
+        <v>28256.914</v>
       </c>
       <c r="D48">
-        <v>22882.926</v>
+        <v>21270.572</v>
       </c>
       <c r="E48">
-        <v>51114.456</v>
+        <v>35243.256</v>
       </c>
       <c r="F48">
-        <v>26549.387</v>
+        <v>16352.3</v>
       </c>
       <c r="G48">
-        <v>16259.624</v>
+        <v>12258.421</v>
       </c>
       <c r="H48">
-        <v>36839.15</v>
+        <v>20446.178</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3531068468.286</v>
+        <v>2174855872.839</v>
       </c>
       <c r="M48">
-        <v>2162530014.001</v>
+        <v>1630370023.244</v>
       </c>
       <c r="N48">
-        <v>4899606922.57</v>
+        <v>2719341722.434</v>
       </c>
     </row>
     <row r="49">
@@ -2690,26 +2690,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C49">
-        <v>21989.039</v>
+        <v>18917.842</v>
       </c>
       <c r="D49">
-        <v>13619.58</v>
+        <v>14130.585</v>
       </c>
       <c r="E49">
-        <v>30358.498</v>
+        <v>23705.098</v>
       </c>
       <c r="F49">
-        <v>9665.412</v>
+        <v>5756.211</v>
       </c>
       <c r="G49">
-        <v>5950.846</v>
+        <v>4260.987</v>
       </c>
       <c r="H49">
-        <v>13379.979</v>
+        <v>7251.435</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1285499820.982</v>
+        <v>765576033.6900001</v>
       </c>
       <c r="M49">
-        <v>791462462.383</v>
+        <v>566711213.051</v>
       </c>
       <c r="N49">
-        <v>1779537179.581</v>
+        <v>964440854.329</v>
       </c>
     </row>
     <row r="50">
@@ -2738,26 +2738,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>8273.421</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>6030.438</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>10516.403</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>451.473</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>309.71</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>593.236</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2769,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>60045948.238</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>41191468.437</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>78900428.039</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,13 +447,13 @@
         <v>526.026</v>
       </c>
       <c r="F2">
-        <v>4277.535</v>
+        <v>25665.207</v>
       </c>
       <c r="G2">
-        <v>3545.256</v>
+        <v>21271.533</v>
       </c>
       <c r="H2">
-        <v>5009.814</v>
+        <v>30058.882</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>568912098.75</v>
+        <v>3413472592.501</v>
       </c>
       <c r="M2">
-        <v>471518988.045</v>
+        <v>2829113928.272</v>
       </c>
       <c r="N2">
-        <v>666305209.455</v>
+        <v>3997831256.729</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>1000.346</v>
       </c>
       <c r="F3">
-        <v>6690.226</v>
+        <v>40141.356</v>
       </c>
       <c r="G3">
-        <v>5628.863</v>
+        <v>33773.18</v>
       </c>
       <c r="H3">
-        <v>7751.589</v>
+        <v>46509.533</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>889800063.336</v>
+        <v>5338800380.015</v>
       </c>
       <c r="M3">
-        <v>748638816.308</v>
+        <v>4491832897.845</v>
       </c>
       <c r="N3">
-        <v>1030961310.364</v>
+        <v>6185767862.186</v>
       </c>
     </row>
     <row r="4">
@@ -543,13 +543,13 @@
         <v>2650.437</v>
       </c>
       <c r="F4">
-        <v>14167.55</v>
+        <v>85005.299</v>
       </c>
       <c r="G4">
-        <v>11942.511</v>
+        <v>71655.064</v>
       </c>
       <c r="H4">
-        <v>16392.589</v>
+        <v>98355.534</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1884284127.071</v>
+        <v>11305704762.425</v>
       </c>
       <c r="M4">
-        <v>1588353924.628</v>
+        <v>9530123547.771</v>
       </c>
       <c r="N4">
-        <v>2180214329.513</v>
+        <v>13081285977.08</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>5654.706</v>
       </c>
       <c r="F5">
-        <v>21942.365</v>
+        <v>131654.192</v>
       </c>
       <c r="G5">
-        <v>18545.553</v>
+        <v>111273.318</v>
       </c>
       <c r="H5">
-        <v>25339.178</v>
+        <v>152035.065</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2918334587.232</v>
+        <v>17510007523.39</v>
       </c>
       <c r="M5">
-        <v>2466558558.969</v>
+        <v>14799351353.815</v>
       </c>
       <c r="N5">
-        <v>3370110615.494</v>
+        <v>20220663692.965</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>12007.059</v>
       </c>
       <c r="F6">
-        <v>29708.925</v>
+        <v>178253.551</v>
       </c>
       <c r="G6">
-        <v>25244.044</v>
+        <v>151464.263</v>
       </c>
       <c r="H6">
-        <v>34173.806</v>
+        <v>205042.838</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>3951287042.824</v>
+        <v>23707722256.944</v>
       </c>
       <c r="M6">
-        <v>3357457834.245</v>
+        <v>20144747005.469</v>
       </c>
       <c r="N6">
-        <v>4545116251.403</v>
+        <v>27270697508.419</v>
       </c>
     </row>
     <row r="7">
@@ -687,13 +687,13 @@
         <v>19432.683</v>
       </c>
       <c r="F7">
-        <v>20719.033</v>
+        <v>124314.197</v>
       </c>
       <c r="G7">
-        <v>17515.616</v>
+        <v>105093.698</v>
       </c>
       <c r="H7">
-        <v>23922.449</v>
+        <v>143534.695</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2755631358.734</v>
+        <v>16533788152.402</v>
       </c>
       <c r="M7">
-        <v>2329576975.778</v>
+        <v>13977461854.667</v>
       </c>
       <c r="N7">
-        <v>3181685741.689</v>
+        <v>19090114450.137</v>
       </c>
     </row>
     <row r="8">
@@ -735,13 +735,13 @@
         <v>26849.578</v>
       </c>
       <c r="F8">
-        <v>3328.982</v>
+        <v>19973.89</v>
       </c>
       <c r="G8">
-        <v>2630.057</v>
+        <v>15780.343</v>
       </c>
       <c r="H8">
-        <v>4027.906</v>
+        <v>24167.437</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>442754567.916</v>
+        <v>2656527407.498</v>
       </c>
       <c r="M8">
-        <v>349797606.028</v>
+        <v>2098785636.166</v>
       </c>
       <c r="N8">
-        <v>535711529.805</v>
+        <v>3214269178.83</v>
       </c>
     </row>
     <row r="9">
@@ -783,13 +783,13 @@
         <v>313.847</v>
       </c>
       <c r="F9">
-        <v>142.563</v>
+        <v>855.047</v>
       </c>
       <c r="G9">
-        <v>87.54600000000001</v>
+        <v>524.896</v>
       </c>
       <c r="H9">
-        <v>197.58</v>
+        <v>1185.198</v>
       </c>
       <c r="I9">
         <v>12618218.994</v>
@@ -801,13 +801,13 @@
         <v>17481925.689</v>
       </c>
       <c r="L9">
-        <v>18960899.212</v>
+        <v>113721247.428</v>
       </c>
       <c r="M9">
-        <v>11643619.096</v>
+        <v>69811173.066</v>
       </c>
       <c r="N9">
-        <v>26278179.327</v>
+        <v>157631321.79</v>
       </c>
     </row>
     <row r="10">
@@ -831,13 +831,13 @@
         <v>662.377</v>
       </c>
       <c r="F10">
-        <v>247.562</v>
+        <v>1485.212</v>
       </c>
       <c r="G10">
-        <v>154.246</v>
+        <v>925.9160000000001</v>
       </c>
       <c r="H10">
-        <v>340.878</v>
+        <v>2044.508</v>
       </c>
       <c r="I10">
         <v>26790745.136</v>
@@ -849,13 +849,13 @@
         <v>36895738.799</v>
       </c>
       <c r="L10">
-        <v>32925748.891</v>
+        <v>197533244.839</v>
       </c>
       <c r="M10">
-        <v>20514662.593</v>
+        <v>123146859.552</v>
       </c>
       <c r="N10">
-        <v>45336835.19</v>
+        <v>271919630.126</v>
       </c>
     </row>
     <row r="11">
@@ -879,13 +879,13 @@
         <v>2155.065</v>
       </c>
       <c r="F11">
-        <v>641.12</v>
+        <v>3847.15</v>
       </c>
       <c r="G11">
-        <v>396.567</v>
+        <v>2378.536</v>
       </c>
       <c r="H11">
-        <v>885.674</v>
+        <v>5315.765</v>
       </c>
       <c r="I11">
         <v>86856760.43700001</v>
@@ -897,13 +897,13 @@
         <v>120041443.325</v>
       </c>
       <c r="L11">
-        <v>85269014.647</v>
+        <v>511671014.332</v>
       </c>
       <c r="M11">
-        <v>52743432.632</v>
+        <v>316345321.307</v>
       </c>
       <c r="N11">
-        <v>117794596.662</v>
+        <v>706996707.357</v>
       </c>
     </row>
     <row r="12">
@@ -927,13 +927,13 @@
         <v>5361.584</v>
       </c>
       <c r="F12">
-        <v>1153.087</v>
+        <v>6919.062</v>
       </c>
       <c r="G12">
-        <v>718.5069999999999</v>
+        <v>4315.21</v>
       </c>
       <c r="H12">
-        <v>1587.668</v>
+        <v>9522.914000000001</v>
       </c>
       <c r="I12">
         <v>216942678.365</v>
@@ -945,13 +945,13 @@
         <v>298650969.17</v>
       </c>
       <c r="L12">
-        <v>153360627.463</v>
+        <v>920235245.1950001</v>
       </c>
       <c r="M12">
-        <v>95561390.245</v>
+        <v>573922924.607</v>
       </c>
       <c r="N12">
-        <v>211159864.681</v>
+        <v>1266547565.783</v>
       </c>
     </row>
     <row r="13">
@@ -975,13 +975,13 @@
         <v>15137.352</v>
       </c>
       <c r="F13">
-        <v>2141.633</v>
+        <v>12851.44</v>
       </c>
       <c r="G13">
-        <v>1370.801</v>
+        <v>8233.681</v>
       </c>
       <c r="H13">
-        <v>2912.465</v>
+        <v>17469.2</v>
       </c>
       <c r="I13">
         <v>620626423.591</v>
@@ -993,13 +993,13 @@
         <v>843180786.696</v>
       </c>
       <c r="L13">
-        <v>284837203.788</v>
+        <v>1709241564.14</v>
       </c>
       <c r="M13">
-        <v>182316499.749</v>
+        <v>1095079558.564</v>
       </c>
       <c r="N13">
-        <v>387357907.827</v>
+        <v>2323403569.716</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>18294.1</v>
       </c>
       <c r="F14">
-        <v>1264.399</v>
+        <v>7585.901</v>
       </c>
       <c r="G14">
-        <v>789.7670000000001</v>
+        <v>4735.229</v>
       </c>
       <c r="H14">
-        <v>1739.031</v>
+        <v>10436.574</v>
       </c>
       <c r="I14">
         <v>742233812.592</v>
@@ -1041,13 +1041,13 @@
         <v>1019017959.21</v>
       </c>
       <c r="L14">
-        <v>168165054.828</v>
+        <v>1008924886.668</v>
       </c>
       <c r="M14">
-        <v>105038981.666</v>
+        <v>629785407.232</v>
       </c>
       <c r="N14">
-        <v>231291127.99</v>
+        <v>1388064366.104</v>
       </c>
     </row>
     <row r="15">
@@ -1071,13 +1071,13 @@
         <v>12121.808</v>
       </c>
       <c r="F15">
-        <v>123.008</v>
+        <v>738.951</v>
       </c>
       <c r="G15">
-        <v>70.733</v>
+        <v>424.039</v>
       </c>
       <c r="H15">
-        <v>175.283</v>
+        <v>1053.863</v>
       </c>
       <c r="I15">
         <v>485577095.838</v>
@@ -1089,19 +1089,19 @@
         <v>675208976.104</v>
       </c>
       <c r="L15">
-        <v>16360014.429</v>
+        <v>98280452.00300001</v>
       </c>
       <c r="M15">
-        <v>9407453.546</v>
+        <v>56397160.686</v>
       </c>
       <c r="N15">
-        <v>23312575.313</v>
+        <v>140163743.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1110,46 +1110,46 @@
         </is>
       </c>
       <c r="C16">
-        <v>6.568</v>
+        <v>1893.67</v>
       </c>
       <c r="D16">
-        <v>0.077</v>
+        <v>54.01</v>
       </c>
       <c r="E16">
-        <v>13.058</v>
+        <v>3733.33</v>
       </c>
       <c r="F16">
-        <v>4.564</v>
+        <v>6357.924</v>
       </c>
       <c r="G16">
-        <v>0.046</v>
+        <v>178.59</v>
       </c>
       <c r="H16">
-        <v>9.082000000000001</v>
+        <v>12537.258</v>
       </c>
       <c r="I16">
-        <v>289549.633</v>
+        <v>28039571.992</v>
       </c>
       <c r="J16">
-        <v>3412.597</v>
+        <v>799733.057</v>
       </c>
       <c r="K16">
-        <v>575686.6679999999</v>
+        <v>55279410.927</v>
       </c>
       <c r="L16">
-        <v>606994.61</v>
+        <v>845603910.308</v>
       </c>
       <c r="M16">
-        <v>6061.979</v>
+        <v>23752498.885</v>
       </c>
       <c r="N16">
-        <v>1207927.24</v>
+        <v>1667455321.732</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1158,46 +1158,46 @@
         </is>
       </c>
       <c r="C17">
-        <v>61.077</v>
+        <v>3254.42</v>
       </c>
       <c r="D17">
-        <v>1.21</v>
+        <v>84.518</v>
       </c>
       <c r="E17">
-        <v>120.945</v>
+        <v>6424.321</v>
       </c>
       <c r="F17">
-        <v>36.158</v>
+        <v>9162.263000000001</v>
       </c>
       <c r="G17">
-        <v>0.711</v>
+        <v>225.47</v>
       </c>
       <c r="H17">
-        <v>71.60599999999999</v>
+        <v>18099.056</v>
       </c>
       <c r="I17">
-        <v>2692718.651</v>
+        <v>48188190.142</v>
       </c>
       <c r="J17">
-        <v>53334.556</v>
+        <v>1251457.002</v>
       </c>
       <c r="K17">
-        <v>5332102.746</v>
+        <v>95124923.28300001</v>
       </c>
       <c r="L17">
-        <v>4809048.126</v>
+        <v>1218580940.237</v>
       </c>
       <c r="M17">
-        <v>94539.11500000001</v>
+        <v>29987455.644</v>
       </c>
       <c r="N17">
-        <v>9523557.137</v>
+        <v>2407174424.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C18">
-        <v>166.543</v>
+        <v>4226.107</v>
       </c>
       <c r="D18">
-        <v>4.799</v>
+        <v>141.743</v>
       </c>
       <c r="E18">
-        <v>328.287</v>
+        <v>8310.471</v>
       </c>
       <c r="F18">
-        <v>81.209</v>
+        <v>9598.352000000001</v>
       </c>
       <c r="G18">
-        <v>2.339</v>
+        <v>309.784</v>
       </c>
       <c r="H18">
-        <v>160.079</v>
+        <v>18886.92</v>
       </c>
       <c r="I18">
-        <v>7342375.398</v>
+        <v>62575965.453</v>
       </c>
       <c r="J18">
-        <v>211557.015</v>
+        <v>2098787.849</v>
       </c>
       <c r="K18">
-        <v>14473193.782</v>
+        <v>123053143.057</v>
       </c>
       <c r="L18">
-        <v>10800830.363</v>
+        <v>1276580864.01</v>
       </c>
       <c r="M18">
-        <v>311105.659</v>
+        <v>41201304.202</v>
       </c>
       <c r="N18">
-        <v>21290555.067</v>
+        <v>2511960423.817</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1254,46 +1254,46 @@
         </is>
       </c>
       <c r="C19">
-        <v>253.554</v>
+        <v>5650.43</v>
       </c>
       <c r="D19">
-        <v>7.288</v>
+        <v>181.535</v>
       </c>
       <c r="E19">
-        <v>499.819</v>
+        <v>11119.325</v>
       </c>
       <c r="F19">
-        <v>91.69499999999999</v>
+        <v>9220.02</v>
       </c>
       <c r="G19">
-        <v>2.656</v>
+        <v>294.407</v>
       </c>
       <c r="H19">
-        <v>180.735</v>
+        <v>18145.633</v>
       </c>
       <c r="I19">
-        <v>11178419.656</v>
+        <v>83665914.92900001</v>
       </c>
       <c r="J19">
-        <v>321300.031</v>
+        <v>2687989.398</v>
       </c>
       <c r="K19">
-        <v>22035539.28</v>
+        <v>164643840.459</v>
       </c>
       <c r="L19">
-        <v>12195441.177</v>
+        <v>1226262660.414</v>
       </c>
       <c r="M19">
-        <v>353190.14</v>
+        <v>39156151.094</v>
       </c>
       <c r="N19">
-        <v>24037692.214</v>
+        <v>2413369169.734</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1302,46 +1302,46 @@
         </is>
       </c>
       <c r="C20">
-        <v>369.127</v>
+        <v>8144.413</v>
       </c>
       <c r="D20">
-        <v>8.795999999999999</v>
+        <v>198.11</v>
       </c>
       <c r="E20">
-        <v>729.4589999999999</v>
+        <v>16090.717</v>
       </c>
       <c r="F20">
-        <v>92.982</v>
+        <v>8656.472</v>
       </c>
       <c r="G20">
-        <v>2.191</v>
+        <v>212.357</v>
       </c>
       <c r="H20">
-        <v>183.773</v>
+        <v>17100.587</v>
       </c>
       <c r="I20">
-        <v>16273723.665</v>
+        <v>120594325.817</v>
       </c>
       <c r="J20">
-        <v>387783.223</v>
+        <v>2933410.333</v>
       </c>
       <c r="K20">
-        <v>32159664.108</v>
+        <v>238255241.301</v>
       </c>
       <c r="L20">
-        <v>12366610.157</v>
+        <v>1151310752.462</v>
       </c>
       <c r="M20">
-        <v>291416.587</v>
+        <v>28243420.984</v>
       </c>
       <c r="N20">
-        <v>24441803.728</v>
+        <v>2274378083.939</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1350,46 +1350,46 @@
         </is>
       </c>
       <c r="C21">
-        <v>274.844</v>
+        <v>5393.558</v>
       </c>
       <c r="D21">
-        <v>8.31</v>
+        <v>165.121</v>
       </c>
       <c r="E21">
-        <v>541.379</v>
+        <v>10621.995</v>
       </c>
       <c r="F21">
-        <v>39.948</v>
+        <v>2734.388</v>
       </c>
       <c r="G21">
-        <v>1.048</v>
+        <v>82.142</v>
       </c>
       <c r="H21">
-        <v>78.848</v>
+        <v>5386.634</v>
       </c>
       <c r="I21">
-        <v>12117066.487</v>
+        <v>79862412.934</v>
       </c>
       <c r="J21">
-        <v>366344.003</v>
+        <v>2444946.704</v>
       </c>
       <c r="K21">
-        <v>23867788.97</v>
+        <v>157279879.164</v>
       </c>
       <c r="L21">
-        <v>5313064.385</v>
+        <v>363673634.004</v>
       </c>
       <c r="M21">
-        <v>139324.422</v>
+        <v>10924898.607</v>
       </c>
       <c r="N21">
-        <v>10486804.348</v>
+        <v>716422369.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1398,46 +1398,46 @@
         </is>
       </c>
       <c r="C22">
-        <v>124.568</v>
+        <v>2151.537</v>
       </c>
       <c r="D22">
-        <v>4.261</v>
+        <v>67.039</v>
       </c>
       <c r="E22">
-        <v>244.874</v>
+        <v>4236.035</v>
       </c>
       <c r="F22">
-        <v>3.638</v>
+        <v>147.918</v>
       </c>
       <c r="G22">
-        <v>0.08</v>
+        <v>3.316</v>
       </c>
       <c r="H22">
-        <v>7.195</v>
+        <v>292.52</v>
       </c>
       <c r="I22">
-        <v>5491819.223</v>
+        <v>31857809.569</v>
       </c>
       <c r="J22">
-        <v>187862.982</v>
+        <v>992652.314</v>
       </c>
       <c r="K22">
-        <v>10795775.465</v>
+        <v>62722966.824</v>
       </c>
       <c r="L22">
-        <v>483843.021</v>
+        <v>19673116.158</v>
       </c>
       <c r="M22">
-        <v>10687.903</v>
+        <v>441093.737</v>
       </c>
       <c r="N22">
-        <v>956998.138</v>
+        <v>38905138.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1446,46 +1446,46 @@
         </is>
       </c>
       <c r="C23">
-        <v>1893.67</v>
+        <v>393.539</v>
       </c>
       <c r="D23">
-        <v>54.01</v>
+        <v>14.379</v>
       </c>
       <c r="E23">
-        <v>3733.33</v>
+        <v>772.699</v>
       </c>
       <c r="F23">
-        <v>1059.163</v>
+        <v>1584.197</v>
       </c>
       <c r="G23">
-        <v>29.842</v>
+        <v>56.965</v>
       </c>
       <c r="H23">
-        <v>2088.485</v>
+        <v>3111.43</v>
       </c>
       <c r="I23">
-        <v>28039571.992</v>
+        <v>29594509.504</v>
       </c>
       <c r="J23">
-        <v>799733.057</v>
+        <v>1081285.756</v>
       </c>
       <c r="K23">
-        <v>55279410.927</v>
+        <v>58107733.253</v>
       </c>
       <c r="L23">
-        <v>140868732.655</v>
+        <v>210698258.56</v>
       </c>
       <c r="M23">
-        <v>3969000.533</v>
+        <v>7576283.12</v>
       </c>
       <c r="N23">
-        <v>277768464.777</v>
+        <v>413820234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1494,46 +1494,46 @@
         </is>
       </c>
       <c r="C24">
-        <v>3254.42</v>
+        <v>639.231</v>
       </c>
       <c r="D24">
-        <v>84.518</v>
+        <v>23.927</v>
       </c>
       <c r="E24">
-        <v>6424.321</v>
+        <v>1254.536</v>
       </c>
       <c r="F24">
-        <v>1526.469</v>
+        <v>2114.368</v>
       </c>
       <c r="G24">
-        <v>38.432</v>
+        <v>78.565</v>
       </c>
       <c r="H24">
-        <v>3014.506</v>
+        <v>4150.171</v>
       </c>
       <c r="I24">
-        <v>48188190.142</v>
+        <v>48070821.225</v>
       </c>
       <c r="J24">
-        <v>1251457.002</v>
+        <v>1799318.2</v>
       </c>
       <c r="K24">
-        <v>95124923.28300001</v>
+        <v>94342324.251</v>
       </c>
       <c r="L24">
-        <v>203020424.026</v>
+        <v>281210984.853</v>
       </c>
       <c r="M24">
-        <v>5111485.68</v>
+        <v>10449203.11</v>
       </c>
       <c r="N24">
-        <v>400929362.373</v>
+        <v>551972766.597</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1542,46 +1542,46 @@
         </is>
       </c>
       <c r="C25">
-        <v>4226.107</v>
+        <v>933.4589999999999</v>
       </c>
       <c r="D25">
-        <v>141.743</v>
+        <v>30.49</v>
       </c>
       <c r="E25">
-        <v>8310.471</v>
+        <v>1836.427</v>
       </c>
       <c r="F25">
-        <v>1599.745</v>
+        <v>2465.619</v>
       </c>
       <c r="G25">
-        <v>51.691</v>
+        <v>82.59099999999999</v>
       </c>
       <c r="H25">
-        <v>3147.799</v>
+        <v>4848.647</v>
       </c>
       <c r="I25">
-        <v>62575965.453</v>
+        <v>70197021.634</v>
       </c>
       <c r="J25">
-        <v>2098787.849</v>
+        <v>2292864.732</v>
       </c>
       <c r="K25">
-        <v>123053143.057</v>
+        <v>138101178.535</v>
       </c>
       <c r="L25">
-        <v>212766022.92</v>
+        <v>327927370.628</v>
       </c>
       <c r="M25">
-        <v>6874843.057</v>
+        <v>10984638.031</v>
       </c>
       <c r="N25">
-        <v>418657202.784</v>
+        <v>644870103.225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1590,46 +1590,46 @@
         </is>
       </c>
       <c r="C26">
-        <v>5650.43</v>
+        <v>1531.21</v>
       </c>
       <c r="D26">
-        <v>181.535</v>
+        <v>63.037</v>
       </c>
       <c r="E26">
-        <v>11119.325</v>
+        <v>2999.384</v>
       </c>
       <c r="F26">
-        <v>1535.848</v>
+        <v>2928.093</v>
       </c>
       <c r="G26">
-        <v>50.468</v>
+        <v>121.474</v>
       </c>
       <c r="H26">
-        <v>3021.229</v>
+        <v>5734.713</v>
       </c>
       <c r="I26">
-        <v>83665914.92900001</v>
+        <v>115148551.285</v>
       </c>
       <c r="J26">
-        <v>2687989.398</v>
+        <v>4740427.401</v>
       </c>
       <c r="K26">
-        <v>164643840.459</v>
+        <v>225556675.169</v>
       </c>
       <c r="L26">
-        <v>204267808.457</v>
+        <v>389436420.784</v>
       </c>
       <c r="M26">
-        <v>6712221.779</v>
+        <v>16156013.926</v>
       </c>
       <c r="N26">
-        <v>401823395.136</v>
+        <v>762716827.643</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1638,46 +1638,46 @@
         </is>
       </c>
       <c r="C27">
-        <v>8144.413</v>
+        <v>2161.861</v>
       </c>
       <c r="D27">
-        <v>198.11</v>
+        <v>119.03</v>
       </c>
       <c r="E27">
-        <v>16090.717</v>
+        <v>4204.693</v>
       </c>
       <c r="F27">
-        <v>1442.859</v>
+        <v>2824.06</v>
       </c>
       <c r="G27">
-        <v>35.141</v>
+        <v>153.218</v>
       </c>
       <c r="H27">
-        <v>2850.576</v>
+        <v>5494.902</v>
       </c>
       <c r="I27">
-        <v>120594325.817</v>
+        <v>162574130.825</v>
       </c>
       <c r="J27">
-        <v>2933410.333</v>
+        <v>8951152.227</v>
       </c>
       <c r="K27">
-        <v>238255241.301</v>
+        <v>316197109.423</v>
       </c>
       <c r="L27">
-        <v>191900182.968</v>
+        <v>375599984.142</v>
       </c>
       <c r="M27">
-        <v>4673814.575</v>
+        <v>20377999.147</v>
       </c>
       <c r="N27">
-        <v>379126551.36</v>
+        <v>730821969.136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1686,46 +1686,46 @@
         </is>
       </c>
       <c r="C28">
-        <v>5393.558</v>
+        <v>689.669</v>
       </c>
       <c r="D28">
-        <v>165.121</v>
+        <v>30.603</v>
       </c>
       <c r="E28">
-        <v>10621.995</v>
+        <v>1348.736</v>
       </c>
       <c r="F28">
-        <v>455.797</v>
+        <v>500.838</v>
       </c>
       <c r="G28">
-        <v>13.969</v>
+        <v>21.781</v>
       </c>
       <c r="H28">
-        <v>897.625</v>
+        <v>979.896</v>
       </c>
       <c r="I28">
-        <v>79862412.934</v>
+        <v>51863836.011</v>
       </c>
       <c r="J28">
-        <v>2444946.704</v>
+        <v>2301338.697</v>
       </c>
       <c r="K28">
-        <v>157279879.164</v>
+        <v>101426333.324</v>
       </c>
       <c r="L28">
-        <v>60620993.733</v>
+        <v>66611492.991</v>
       </c>
       <c r="M28">
-        <v>1857857.621</v>
+        <v>2896870.779</v>
       </c>
       <c r="N28">
-        <v>119384129.845</v>
+        <v>130326115.203</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1734,46 +1734,46 @@
         </is>
       </c>
       <c r="C29">
-        <v>2151.537</v>
+        <v>28.229</v>
       </c>
       <c r="D29">
-        <v>67.039</v>
+        <v>0.746</v>
       </c>
       <c r="E29">
-        <v>4236.035</v>
+        <v>55.711</v>
       </c>
       <c r="F29">
-        <v>24.63</v>
+        <v>3.718</v>
       </c>
       <c r="G29">
-        <v>0.556</v>
+        <v>0.024</v>
       </c>
       <c r="H29">
-        <v>48.704</v>
+        <v>7.412</v>
       </c>
       <c r="I29">
-        <v>31857809.569</v>
+        <v>2122836.653</v>
       </c>
       <c r="J29">
-        <v>992652.314</v>
+        <v>56114.641</v>
       </c>
       <c r="K29">
-        <v>62722966.824</v>
+        <v>4189558.665</v>
       </c>
       <c r="L29">
-        <v>3275776.693</v>
+        <v>494481.571</v>
       </c>
       <c r="M29">
-        <v>73906.535</v>
+        <v>3160.369</v>
       </c>
       <c r="N29">
-        <v>6477646.851</v>
+        <v>985802.772</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1782,46 +1782,46 @@
         </is>
       </c>
       <c r="C30">
-        <v>393.539</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>14.379</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>772.699</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>263.924</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>9.448</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>518.4</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>29594509.504</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>1081285.756</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>58107733.253</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>35101930.436</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>1256627.863</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>68947233.01000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1830,46 +1830,46 @@
         </is>
       </c>
       <c r="C31">
-        <v>639.231</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>23.927</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>1254.536</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>352.164</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>13.485</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>690.843</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>48070821.225</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1799318.2</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>94342324.251</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>46837791.091</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>1793502.857</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>91882079.32600001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1878,46 +1878,46 @@
         </is>
       </c>
       <c r="C32">
-        <v>933.4589999999999</v>
+        <v>141.818</v>
       </c>
       <c r="D32">
-        <v>30.49</v>
+        <v>103.498</v>
       </c>
       <c r="E32">
-        <v>1836.427</v>
+        <v>180.138</v>
       </c>
       <c r="F32">
-        <v>410.978</v>
+        <v>1120.26</v>
       </c>
       <c r="G32">
-        <v>13.805</v>
+        <v>817.562</v>
       </c>
       <c r="H32">
-        <v>808.151</v>
+        <v>1422.957</v>
       </c>
       <c r="I32">
-        <v>70197021.634</v>
+        <v>2388071.387</v>
       </c>
       <c r="J32">
-        <v>2292864.732</v>
+        <v>1742802.269</v>
       </c>
       <c r="K32">
-        <v>138101178.535</v>
+        <v>3033340.506</v>
       </c>
       <c r="L32">
-        <v>54660115.408</v>
+        <v>148994532.917</v>
       </c>
       <c r="M32">
-        <v>1836082.406</v>
+        <v>108735739.817</v>
       </c>
       <c r="N32">
-        <v>107484148.41</v>
+        <v>189253326.017</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1926,46 +1926,46 @@
         </is>
       </c>
       <c r="C33">
-        <v>1531.21</v>
+        <v>314.77</v>
       </c>
       <c r="D33">
-        <v>63.037</v>
+        <v>229.795</v>
       </c>
       <c r="E33">
-        <v>2999.384</v>
+        <v>399.745</v>
       </c>
       <c r="F33">
-        <v>487.974</v>
+        <v>1852.511</v>
       </c>
       <c r="G33">
-        <v>20.235</v>
+        <v>1351.168</v>
       </c>
       <c r="H33">
-        <v>955.7140000000001</v>
+        <v>2353.853</v>
       </c>
       <c r="I33">
-        <v>115148551.285</v>
+        <v>5300411.263</v>
       </c>
       <c r="J33">
-        <v>4740427.401</v>
+        <v>3869515.879</v>
       </c>
       <c r="K33">
-        <v>225556675.169</v>
+        <v>6731306.647</v>
       </c>
       <c r="L33">
-        <v>64900554.932</v>
+        <v>246383927.469</v>
       </c>
       <c r="M33">
-        <v>2691203.845</v>
+        <v>179705385.365</v>
       </c>
       <c r="N33">
-        <v>127109906.019</v>
+        <v>313062469.572</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1974,46 +1974,46 @@
         </is>
       </c>
       <c r="C34">
-        <v>2161.861</v>
+        <v>1746.884</v>
       </c>
       <c r="D34">
-        <v>119.03</v>
+        <v>1285.847</v>
       </c>
       <c r="E34">
-        <v>4204.693</v>
+        <v>2207.921</v>
       </c>
       <c r="F34">
-        <v>470.348</v>
+        <v>6473.187</v>
       </c>
       <c r="G34">
-        <v>25.387</v>
+        <v>4763.048</v>
       </c>
       <c r="H34">
-        <v>915.309</v>
+        <v>8183.326</v>
       </c>
       <c r="I34">
-        <v>162574130.825</v>
+        <v>29415776.364</v>
       </c>
       <c r="J34">
-        <v>8951152.227</v>
+        <v>21652372.327</v>
       </c>
       <c r="K34">
-        <v>316197109.423</v>
+        <v>37179180.4</v>
       </c>
       <c r="L34">
-        <v>62556260.732</v>
+        <v>860933863.251</v>
       </c>
       <c r="M34">
-        <v>3376481.394</v>
+        <v>633485414.148</v>
       </c>
       <c r="N34">
-        <v>121736040.07</v>
+        <v>1088382312.353</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2022,46 +2022,46 @@
         </is>
       </c>
       <c r="C35">
-        <v>689.669</v>
+        <v>5026.901</v>
       </c>
       <c r="D35">
-        <v>30.603</v>
+        <v>3670.677</v>
       </c>
       <c r="E35">
-        <v>1348.736</v>
+        <v>6383.125</v>
       </c>
       <c r="F35">
-        <v>83.532</v>
+        <v>9305.83</v>
       </c>
       <c r="G35">
-        <v>3.596</v>
+        <v>6779.557</v>
       </c>
       <c r="H35">
-        <v>163.468</v>
+        <v>11832.102</v>
       </c>
       <c r="I35">
-        <v>51863836.011</v>
+        <v>84647985.89399999</v>
       </c>
       <c r="J35">
-        <v>2301338.697</v>
+        <v>61810522.29</v>
       </c>
       <c r="K35">
-        <v>101426333.324</v>
+        <v>107485449.498</v>
       </c>
       <c r="L35">
-        <v>11109792.267</v>
+        <v>1237675352.88</v>
       </c>
       <c r="M35">
-        <v>478312.001</v>
+        <v>901681118.9859999</v>
       </c>
       <c r="N35">
-        <v>21741272.534</v>
+        <v>1573669586.773</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2070,46 +2070,46 @@
         </is>
       </c>
       <c r="C36">
-        <v>28.229</v>
+        <v>6174.745</v>
       </c>
       <c r="D36">
-        <v>0.746</v>
+        <v>4422.135</v>
       </c>
       <c r="E36">
-        <v>55.711</v>
+        <v>7927.355</v>
       </c>
       <c r="F36">
-        <v>0.619</v>
+        <v>1840.244</v>
       </c>
       <c r="G36">
-        <v>0.005</v>
+        <v>1255.407</v>
       </c>
       <c r="H36">
-        <v>1.234</v>
+        <v>2425.082</v>
       </c>
       <c r="I36">
-        <v>2122836.653</v>
+        <v>103976530.028</v>
       </c>
       <c r="J36">
-        <v>56114.641</v>
+        <v>74464325.168</v>
       </c>
       <c r="K36">
-        <v>4189558.665</v>
+        <v>133488734.888</v>
       </c>
       <c r="L36">
-        <v>82376.85799999999</v>
+        <v>244752485.393</v>
       </c>
       <c r="M36">
-        <v>669.797</v>
+        <v>166969112.034</v>
       </c>
       <c r="N36">
-        <v>164083.919</v>
+        <v>322535858.752</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>23404.286</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>17200.907</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>29607.665</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>122096.686</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>89181.22900000001</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>155012.143</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,19 +2145,19 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>16238859222.701</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>11861103476.261</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>20616614969.141</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>25167.979</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>18613.18</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>31722.777</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>109687.022</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>80789.503</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>138584.541</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,19 +2193,19 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>14588373876.949</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>10745003859.067</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>18431743894.832</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2214,46 +2214,46 @@
         </is>
       </c>
       <c r="C39">
-        <v>141.818</v>
+        <v>24143.745</v>
       </c>
       <c r="D39">
-        <v>103.498</v>
+        <v>17870.784</v>
       </c>
       <c r="E39">
-        <v>180.138</v>
+        <v>30416.705</v>
       </c>
       <c r="F39">
-        <v>186.677</v>
+        <v>84965.308</v>
       </c>
       <c r="G39">
-        <v>136.181</v>
+        <v>62507.139</v>
       </c>
       <c r="H39">
-        <v>237.173</v>
+        <v>107423.478</v>
       </c>
       <c r="I39">
-        <v>2388071.387</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1742802.269</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>3033340.506</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>24828021.818</v>
+        <v>11300386001.51</v>
       </c>
       <c r="M39">
-        <v>18112028.585</v>
+        <v>8313449484.458</v>
       </c>
       <c r="N39">
-        <v>31544015.051</v>
+        <v>14287322518.562</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,46 +2262,46 @@
         </is>
       </c>
       <c r="C40">
-        <v>314.77</v>
+        <v>23301.198</v>
       </c>
       <c r="D40">
-        <v>229.795</v>
+        <v>17346.353</v>
       </c>
       <c r="E40">
-        <v>399.745</v>
+        <v>29256.043</v>
       </c>
       <c r="F40">
-        <v>308.696</v>
+        <v>59950.621</v>
       </c>
       <c r="G40">
-        <v>225.191</v>
+        <v>44461.102</v>
       </c>
       <c r="H40">
-        <v>392.202</v>
+        <v>75440.14</v>
       </c>
       <c r="I40">
-        <v>5300411.263</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>3869515.879</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>6731306.647</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>41056584.651</v>
+        <v>7973432536.489</v>
       </c>
       <c r="M40">
-        <v>29950347.074</v>
+        <v>5913326517.921</v>
       </c>
       <c r="N40">
-        <v>52162822.227</v>
+        <v>10033538555.057</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2310,46 +2310,46 @@
         </is>
       </c>
       <c r="C41">
-        <v>1746.884</v>
+        <v>28256.914</v>
       </c>
       <c r="D41">
-        <v>1285.847</v>
+        <v>21270.572</v>
       </c>
       <c r="E41">
-        <v>2207.921</v>
+        <v>35243.256</v>
       </c>
       <c r="F41">
-        <v>1078.871</v>
+        <v>49068.691</v>
       </c>
       <c r="G41">
-        <v>793.683</v>
+        <v>36795.152</v>
       </c>
       <c r="H41">
-        <v>1364.06</v>
+        <v>61342.231</v>
       </c>
       <c r="I41">
-        <v>29415776.364</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>21652372.327</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>37179180.4</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>143489868.587</v>
+        <v>6526135931.784</v>
       </c>
       <c r="M41">
-        <v>105559813.708</v>
+        <v>4893755183.777</v>
       </c>
       <c r="N41">
-        <v>181419923.467</v>
+        <v>8158516679.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2358,46 +2358,46 @@
         </is>
       </c>
       <c r="C42">
-        <v>5026.901</v>
+        <v>18917.842</v>
       </c>
       <c r="D42">
-        <v>3670.677</v>
+        <v>14130.585</v>
       </c>
       <c r="E42">
-        <v>6383.125</v>
+        <v>23705.098</v>
       </c>
       <c r="F42">
-        <v>1550.71</v>
+        <v>17288.345</v>
       </c>
       <c r="G42">
-        <v>1129.844</v>
+        <v>12807.107</v>
       </c>
       <c r="H42">
-        <v>1971.577</v>
+        <v>21769.583</v>
       </c>
       <c r="I42">
-        <v>84647985.89399999</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>61810522.29</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>107485449.498</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>206244472.576</v>
+        <v>2299349895.343</v>
       </c>
       <c r="M42">
-        <v>150269218.668</v>
+        <v>1703345215.93</v>
       </c>
       <c r="N42">
-        <v>262219726.483</v>
+        <v>2895354574.756</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2406,376 +2406,40 @@
         </is>
       </c>
       <c r="C43">
-        <v>6174.745</v>
+        <v>8273.421</v>
       </c>
       <c r="D43">
-        <v>4422.135</v>
+        <v>6030.438</v>
       </c>
       <c r="E43">
-        <v>7927.355</v>
+        <v>10516.403</v>
       </c>
       <c r="F43">
-        <v>306.792</v>
+        <v>1354.743</v>
       </c>
       <c r="G43">
-        <v>209.592</v>
+        <v>932.453</v>
       </c>
       <c r="H43">
-        <v>403.993</v>
+        <v>1777.033</v>
       </c>
       <c r="I43">
-        <v>103976530.028</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>74464325.168</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>133488734.888</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>40803386.096</v>
+        <v>180180848.313</v>
       </c>
       <c r="M43">
-        <v>27875711.287</v>
+        <v>124016302.797</v>
       </c>
       <c r="N43">
-        <v>53731060.905</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>23404.286</v>
-      </c>
-      <c r="D44">
-        <v>17200.907</v>
-      </c>
-      <c r="E44">
-        <v>29607.665</v>
-      </c>
-      <c r="F44">
-        <v>40737.83</v>
-      </c>
-      <c r="G44">
-        <v>29788.922</v>
-      </c>
-      <c r="H44">
-        <v>51686.737</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>5418131360.702</v>
-      </c>
-      <c r="M44">
-        <v>3961926648.764</v>
-      </c>
-      <c r="N44">
-        <v>6874336072.64</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>25167.979</v>
-      </c>
-      <c r="D45">
-        <v>18613.18</v>
-      </c>
-      <c r="E45">
-        <v>31722.777</v>
-      </c>
-      <c r="F45">
-        <v>36597.704</v>
-      </c>
-      <c r="G45">
-        <v>26926.396</v>
-      </c>
-      <c r="H45">
-        <v>46269.013</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>4867494659.078</v>
-      </c>
-      <c r="M45">
-        <v>3581210651.977</v>
-      </c>
-      <c r="N45">
-        <v>6153778666.179</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>24143.745</v>
-      </c>
-      <c r="D46">
-        <v>17870.784</v>
-      </c>
-      <c r="E46">
-        <v>30416.705</v>
-      </c>
-      <c r="F46">
-        <v>28323.726</v>
-      </c>
-      <c r="G46">
-        <v>20837.751</v>
-      </c>
-      <c r="H46">
-        <v>35809.701</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>3767055556.298</v>
-      </c>
-      <c r="M46">
-        <v>2771420924.548</v>
-      </c>
-      <c r="N46">
-        <v>4762690188.049</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>23301.198</v>
-      </c>
-      <c r="D47">
-        <v>17346.353</v>
-      </c>
-      <c r="E47">
-        <v>29256.043</v>
-      </c>
-      <c r="F47">
-        <v>19982.586</v>
-      </c>
-      <c r="G47">
-        <v>14790.738</v>
-      </c>
-      <c r="H47">
-        <v>25174.435</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>2657683982.743</v>
-      </c>
-      <c r="M47">
-        <v>1967168132.255</v>
-      </c>
-      <c r="N47">
-        <v>3348199833.231</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>28256.914</v>
-      </c>
-      <c r="D48">
-        <v>21270.572</v>
-      </c>
-      <c r="E48">
-        <v>35243.256</v>
-      </c>
-      <c r="F48">
-        <v>16352.3</v>
-      </c>
-      <c r="G48">
-        <v>12258.421</v>
-      </c>
-      <c r="H48">
-        <v>20446.178</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>2174855872.839</v>
-      </c>
-      <c r="M48">
-        <v>1630370023.244</v>
-      </c>
-      <c r="N48">
-        <v>2719341722.434</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>18917.842</v>
-      </c>
-      <c r="D49">
-        <v>14130.585</v>
-      </c>
-      <c r="E49">
-        <v>23705.098</v>
-      </c>
-      <c r="F49">
-        <v>5756.211</v>
-      </c>
-      <c r="G49">
-        <v>4260.987</v>
-      </c>
-      <c r="H49">
-        <v>7251.435</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>765576033.6900001</v>
-      </c>
-      <c r="M49">
-        <v>566711213.051</v>
-      </c>
-      <c r="N49">
-        <v>964440854.329</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>8273.421</v>
-      </c>
-      <c r="D50">
-        <v>6030.438</v>
-      </c>
-      <c r="E50">
-        <v>10516.403</v>
-      </c>
-      <c r="F50">
-        <v>451.473</v>
-      </c>
-      <c r="G50">
-        <v>309.71</v>
-      </c>
-      <c r="H50">
-        <v>593.236</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>60045948.238</v>
-      </c>
-      <c r="M50">
-        <v>41191468.437</v>
-      </c>
-      <c r="N50">
-        <v>78900428.039</v>
+        <v>236345393.829</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age_Rubin.xlsx
@@ -377,7 +377,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_sup</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -392,7 +392,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>tot_daly_sup</t>
+          <t>tot_daly_up</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>tot_medic_costs_sup</t>
+          <t>tot_medic_costs_up</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -422,7 +422,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>tot_soc_costs_sup</t>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
